--- a/reports/2026-09-17__daily-marker.xlsx
+++ b/reports/2026-09-17__daily-marker.xlsx
@@ -9,22 +9,26 @@
   <sheets>
     <sheet name="Index" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Availability" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Peer gap" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Earnings window" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Cohort index" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Depletion" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Promo diff" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Promo reference" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Booking curve" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Final payment" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Peer gap" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Earnings window" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cohort index" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Depletion" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Promo diff" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Promo reference" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Index'!$A$42:$G$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Index'!$A$44:$G$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Availability'!$A$15:$P$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Peer gap'!$A$17:$L$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Earnings window'!$A$11:$I$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cohort index'!$A$17:$S$115</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Depletion'!$A$15:$U$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Promo diff'!$A$15:$R$63</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Promo reference'!$A$14:$Q$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Booking curve'!$A$22:$T$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Final payment'!$A$16:$R$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Peer gap'!$A$18:$L$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Earnings window'!$A$11:$I$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cohort index'!$A$17:$S$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Depletion'!$A$15:$U$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Promo diff'!$A$15:$R$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Promo reference'!$A$14:$Q$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -616,7 +620,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-17T06:51:38+00:00</t>
+          <t>2026-09-17T20:11:08+00:00</t>
         </is>
       </c>
     </row>
@@ -699,12 +703,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Peer gap</t>
+          <t>Booking curve</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>peer-gap</t>
+          <t>booking-curve</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -713,7 +717,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -722,19 +726,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NCLH vs peer median pppn, per region and cabin category, on cruise-only rows.</t>
+          <t>Price, dispersion and sold-out share against days to departure, per region: 7-8 night, cruise-only, suites and non-peer-comparable cabins excluded. Bands are 15 days near departure, where fares move, and widen further out.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Earnings window</t>
+          <t>Final payment</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>earnings-window</t>
+          <t>final-payment</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -752,28 +756,28 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sailings departing inside the NCLH print window vs outside it. Split on sail date, not collection date.</t>
+          <t>Do fares and sold-out share jump as sailings cross final payment? A cutoff SCAN, so the boundary is located rather than assumed. Check peer_own_jump_pct before reading any row: where the control jumps too, the cutoff has caught the calendar.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cohort index</t>
+          <t>Peer gap</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>cohort-index</t>
+          <t>peer-gap</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>all scrape dates in the tier</t>
+          <t>this scrape date</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -782,28 +786,28 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Since-inception index on a MATCHED BASKET of cabins, with the naive all-rows index beside it. index_matched cannot be moved by sailings entering the book; mix_effect_pp is how much of the naive move is composition rather than price.</t>
+          <t>NCLH vs peer median pppn, per region and cabin category, on cruise-only rows.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Depletion</t>
+          <t>Earnings window</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>depletion</t>
+          <t>earnings-window</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>all scrape dates in the tier</t>
+          <t>this scrape date</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -812,19 +816,19 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Change in closed share per day. Needs &gt;=2 collection dates or it reports nothing rather than inventing a slope.</t>
+          <t>Sailings departing inside the NCLH print window vs outside it. Split on sail date, not collection date.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Promo diff</t>
+          <t>Cohort index</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>promo-diff</t>
+          <t>cohort-index</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -833,7 +837,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -842,140 +846,160 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Which offers widened, narrowed, appeared or were withdrawn between dates, by reach on cabins seen both times.</t>
+          <t>Since-inception index on a MATCHED BASKET of cabins, with the naive all-rows index beside it. index_matched cannot be moved by sailings entering the book; mix_effect_pp is how much of the naive move is composition rather than price.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Depletion</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>depletion</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>all scrape dates in the tier</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>24</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Change in closed share per day. Needs &gt;=2 collection dates or it reports nothing rather than inventing a slope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Promo diff</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>promo-diff</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>all scrape dates in the tier</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>48</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Which offers widened, narrowed, appeared or were withdrawn between dates, by reach on cabins seen both times.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Promo reference</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>promo-reference</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>reference (every date in the tier)</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D28" t="n">
         <v>15</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>The decoder ring: every offer observed, in the vendor's own words, with its reach and scope. Read the Promo diff against this rather than against a hash.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Region coverage on this basis</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Every region the config asks for, including those that returned nothing. A region with 0 rows is absent from every sheet; without this table that is indistinguishable from a region nobody requested.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>observations</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>sailings</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>lines</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>package_rows</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Caribbean</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>467</v>
-      </c>
-      <c r="C32" t="n">
-        <v>104</v>
-      </c>
-      <c r="D32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Southern Europe</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>79</v>
-      </c>
-      <c r="C33" t="n">
-        <v>14</v>
-      </c>
-      <c r="D33" t="n">
-        <v>2</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10</v>
+        <v>467</v>
       </c>
       <c r="C34" t="n">
+        <v>104</v>
+      </c>
+      <c r="D34" t="n">
         <v>2</v>
-      </c>
-      <c r="D34" t="n">
-        <v>1</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -985,14 +1009,14 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Bermuda</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D35" t="n">
         <v>2</v>
@@ -1005,131 +1029,1535 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaska</t>
+          <t>Northern Europe</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>no rows on this basis -- absent from every sheet</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>34</v>
+      </c>
+      <c r="C37" t="n">
+        <v>6</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Alaska</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>no rows on this basis -- absent from every sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Transatlantic</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="inlineStr">
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>no rows on this basis -- absent from every sheet</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Scope comparability between collection dates</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Whether each pair of adjacent collection dates sampled the same population. Where `comparable` is NO, the collector itself changed, and every slope or index spanning that pair is measuring the change to the collector as well as the market.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>from_date</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>to_date</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>sailings_before</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>sailings_after</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>sailings_delta_pct</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>comparable</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>why_not</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="C45" t="n">
         <v>113</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D45" t="n">
         <v>126</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="E45" s="6" t="n">
         <v>11.5</v>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A42:G43"/>
+  <autoFilter ref="A44:G45"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="46" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Promo reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>The decoder ring: every offer observed, in the vendor's own words, with its reach and scope. Read the Promo diff against this rather than against a hash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Time scope: reference (every date in the tier).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>[daily-marker] sail 2026-10-01..2026-12-31 | regions: Bermuda, Caribbean, Northern Europe, Southern Europe | observed 2026-09-16..2026-09-17 | 1152 obs / 146 sailings | granularity: category</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>! daily-marker is the Oct-Dec 2026 near-term cohort, and its region mix is set by seasonal deployment, not by sampling choice. Measured from the near-term universe on 2026-09-15: Caribbean 104 eligible itineraries (85 NCL / 19 Carnival); Southern Europe 15, ALL NCL, all departing October-early November, 0 in December and 0 on Carnival; Alaska 0. So cross-line work in this tier is Caribbean-only, and its Southern Europe rows are a single-line October series that dies when the Mediterranean season ends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>! PEER-COMPARABLE REGIONS in this basis: Bermuda, Caribbean, Southern Europe. Single-line only (no peer rows, so no cross-line claim can rest on them): Northern Europe (Norwegian Cruise Line).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>! NOT ALL LINES PUBLISH OFFERS: Carnival Cruise Line, Royal Caribbean International expose no promo detail at all, so their absence from this table is a gap in the source, not evidence that they are not discounting. Any cross-line read on promotion intensity is one-sided.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>- One row per (line, offer code). A promo_hash is a bundle of offers, so one bundle contributes to several rows; `bundles` counts how many distinct bundles carried this offer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>- share_of_line_cells is out of ALL that line's cells in scope, priced or not, so it reads as reach across the book.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>- `inclusion` = Mandatory means the vendor applies it automatically; it is a headline fare condition, not an opt-in the shopper chose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>- Text is the vendor's own, verbatim from the archived payload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>inclusion</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>offer_type</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>featured</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>cells</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>share_of_line_cells</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>regions</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>cabin_categories</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>n_ships</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>bundles</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>first_scrape</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>last_scrape</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>sail_from</t>
+        </is>
+      </c>
+      <c r="P14" s="5" t="inlineStr">
+        <is>
+          <t>sail_to</t>
+        </is>
+      </c>
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>50-off-all-cruises-offer</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>50% Off All Cruises</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>auto-included-offer</t>
+        </is>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>442</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.8185</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Bermuda, Caribbean, Northern Europe, Southern Europe</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>balcony, inside, oceanview, suite</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>11</v>
+      </c>
+      <c r="L15" t="n">
+        <v>10</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Save big with 50% off cruise fares for all guests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>travel-protection-norwegiancare</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Travel Protection | NorwegianCare</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>travel-protection-offer</t>
+        </is>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>442</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.8185</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Bermuda, Caribbean, Northern Europe, Southern Europe</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>balcony, inside, oceanview, suite</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>11</v>
+      </c>
+      <c r="L16" t="n">
+        <v>10</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Travel
+Protection can help with unforeseen circumstances and get your trip covered
+from shore to ship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>travel-protection-essentials</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Travel Protection | Essentials</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>travel-protection-offer</t>
+        </is>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>442</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>0.8185</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Bermuda, Caribbean, Northern Europe, Southern Europe</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>balcony, inside, oceanview, suite</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>11</v>
+      </c>
+      <c r="L17" t="n">
+        <v>10</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Travel Protection | Essentials</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prepaid-service-charges</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Prepaid Service Charges</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>prepaid-service-charge-offer</t>
+        </is>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>442</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.8185</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Bermuda, Caribbean, Northern Europe, Southern Europe</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>balcony, inside, oceanview, suite</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>11</v>
+      </c>
+      <c r="L18" t="n">
+        <v>10</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Prepaying gratuities can provide peace of mind for a smoother cruise experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>50-pct-Off-All-Cruises-Offer</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>50% Off All Cruises</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>stateroom-offer</t>
+        </is>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>442</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.8185</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Bermuda, Caribbean, Northern Europe, Southern Europe</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>balcony, inside, oceanview, suite</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>11</v>
+      </c>
+      <c r="L19" t="n">
+        <v>10</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Save big with 50% off cruise fares for all guests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>unlimited-open-bar-offer</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Bar</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>beverage-package-offer</t>
+        </is>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>442</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0.8185</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Bermuda, Caribbean, Northern Europe, Southern Europe</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>balcony, inside, oceanview, suite</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>11</v>
+      </c>
+      <c r="L20" t="n">
+        <v>10</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Enjoy the best beverage package at sea! Indulge in unlimited
+premium spirits such as Grey Goose, Casamigos, Woodford Reserve and more, plus
+cocktails, wine, beer, soft drinks and juice — all included. Simply pay the
+package gratuities in advance, and the drinks are on us. With drinks on board
+averaging $15 each, there’s no better value.&lt;/p&gt;&lt;p&gt;Gratuities are $32 per person, per day for 2–5 night
+sailings and $28.50 per person, per day for sailings of 6 nights or more. This
+is reflected in the total price shown above and in the guest breakdown.&lt;br&gt;&lt;/p&gt;&lt;p&gt;The package applies to all guests in the stateroom aged 21+.
+Guests 1 or 2 under age 21 will instead receive juice and unlimited fountain
+soda for $12.50 per person per day. Guests 3–8 under 21 will not receive a
+beverage package but may purchase one separately.&lt;/p&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>specialty-dining-offer</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Dining</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>dining-offer</t>
+        </is>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>442</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.8185</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Bermuda, Caribbean, Northern Europe, Southern Europe</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>balcony, inside, oceanview, suite</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>11</v>
+      </c>
+      <c r="L21" t="n">
+        <v>10</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Savor amazing multi-course meals at our award-winning Specialty Restaurants, such as Cagney’s Steakhouse or Le Bistro. Enjoy elevated dining experiences featuring globally inspired cuisine and exceptional service — all included. Simply pre-pay the package gratuities in advance, and the dining experience is on us. With an average of $60 per meal onboard, this value can’t be beat. &lt;br&gt;  &lt;br&gt;   The package applies to all guests on the reservation.  Guests under age 13 dine for free when ordering from the kids’ menu. If they choose to order from the specialty dining menu, a $20 cover charge will apply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>free-wifi-offer</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Wi-Fi Package</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>wifi-package-offer</t>
+        </is>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>442</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.8185</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Bermuda, Caribbean, Northern Europe, Southern Europe</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>balcony, inside, oceanview, suite</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>11</v>
+      </c>
+      <c r="L22" t="n">
+        <v>10</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Stay connected throughout your cruise with 150 minutes of hi-speed Wi-Fi per person included. Offer applies to all guests in the stateroom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>excursion-credits-offer</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Excursion Credits</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>shorex-offer</t>
+        </is>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>442</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>0.8185</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Bermuda, Caribbean, Northern Europe, Southern Europe</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>balcony, inside, oceanview, suite</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>11</v>
+      </c>
+      <c r="L23" t="n">
+        <v>10</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Receive a $50 credit toward every shore excursion. Offer applies to the first guest on the reservation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>specialty-dining-offer-7-8-nights</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Dining</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>dining-offer</t>
+        </is>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>379</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.7019</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Bermuda, Caribbean, Southern Europe</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>balcony, inside, oceanview, suite</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>8</v>
+      </c>
+      <c r="L24" t="n">
+        <v>5</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Savor 3 amazing multi-course meals at our award-winning Specialty Restaurants, such as Cagney’s Steakhouse or Le Bistro. Enjoy elevated dining experiences featuring globally inspired cuisine and exceptional service — all included. Simply pre-pay the package gratuities in advance, and the dining experience is on us. With an average of $60 per meal onboard, this value can’t be beat. &lt;br&gt;  &lt;br&gt;  The package applies to all guests on the reservation.  Guests under age 13 dine for free when ordering from the kids’ menu. If they choose to order from the specialty dining menu, a $20 cover charge will apply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kids-Sail-Free-Offer</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Kids Sail Free</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>auto-included-offer</t>
+        </is>
+      </c>
+      <c r="F25" t="b">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>280</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.5185</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Bermuda, Caribbean, Southern Europe</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>balcony, inside, oceanview, suite</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>9</v>
+      </c>
+      <c r="L25" t="n">
+        <v>5</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2026-12-13</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>3rd &amp; 4th guests in the same stateroom pay only taxes, and fees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Past-Guest-Offer</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Past Guest Offer</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>auto-included-offer</t>
+        </is>
+      </c>
+      <c r="F26" t="b">
+        <v>1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>64</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>0.1185</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Bermuda, Caribbean, Southern Europe</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>balcony, inside, oceanview, suite</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>6</v>
+      </c>
+      <c r="L26" t="n">
+        <v>4</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-12-13</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Extra Latitudes Point</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>specialty-dining-offer-9-nights</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Dining</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>dining-offer</t>
+        </is>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>47</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Northern Europe, Southern Europe</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>balcony, inside, oceanview, suite</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Savor 4 amazing multi-course meals at our award-winning Specialty Restaurants, such as Cagney’s Steakhouse or Le Bistro. Enjoy elevated dining experiences featuring globally inspired cuisine and exceptional service — all included. Simply pre-pay the package gratuities in advance, and the dining experience is on us. With an average of $60 per meal onboard, this value can’t be beat.&lt;br&gt;   &lt;br&gt;    The package applies to all guests on the reservation.  Guests under age 13 dine for free when ordering from the kids’ menu. If they choose to order from the specialty dining menu, a $20 cover charge will apply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>specialty-dining-offer-5-6-nights</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Dining</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>dining-offer</t>
+        </is>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>16</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>0.0296</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Bermuda, Caribbean</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>balcony, inside, oceanview, suite</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" t="n">
+        <v>3</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Savor 2 amazing multi-course meals at our award-winning Specialty Restaurants, such as Cagney’s Steakhouse or Le Bistro. Enjoy elevated dining experiences featuring globally inspired cuisine and exceptional service — all included. Simply pre-pay the package gratuities in advance, and the dining experience is on us. With an average of $60 per meal onboard, this value can’t be beat.&lt;br&gt; &lt;br&gt; The package applies to all guests on the reservation.  Guests under age 13 dine for free when ordering from the kids’ menu. If they choose to order from the specialty dining menu, a $20 cover charge will apply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>latitudes-rewards-members-cruise</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Latitudes Annual Member Cruise</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>auto-included-offer</t>
+        </is>
+      </c>
+      <c r="F29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>12</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>balcony, inside, oceanview, suite</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2026-12-06</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2026-12-06</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Latitudes Member Cruise</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A14:Q29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2957,7 +4385,2300 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:T33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="27" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Booking curve</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Price, dispersion and sold-out share against days to departure, per region: 7-8 night, cruise-only, suites and non-peer-comparable cabins excluded. Bands are 15 days near departure, where fares move, and widen further out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Time scope: this scrape date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>[daily-marker] sail 2026-10-04..2026-12-27 | regions: Bermuda, Caribbean, Southern Europe | observed 2026-09-17 | 123 obs / 33 sailings | granularity: category</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>! daily-marker is the Oct-Dec 2026 near-term cohort, and its region mix is set by seasonal deployment, not by sampling choice. Measured from the near-term universe on 2026-09-15: Caribbean 104 eligible itineraries (85 NCL / 19 Carnival); Southern Europe 15, ALL NCL, all departing October-early November, 0 in December and 0 on Carnival; Alaska 0. So cross-line work in this tier is Caribbean-only, and its Southern Europe rows are a single-line October series that dies when the Mediterranean season ends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>! PEER-COMPARABLE REGIONS in this basis: Southern Europe. Single-line only (no peer rows, so no cross-line claim can rest on them): Bermuda (Norwegian Cruise Line), Caribbean (Norwegian Cruise Line).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>! PRODUCT FILTER: cruise-only. Of 522 priced rows in scope, 522 are cruise-only, 0 are land+cruise packages (excluded), 0 are unclassified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>! PEER-COMPARABLE CABINS ONLY: dropped MINISUITE. These are filed under a peer category but are not the same product as the peer's version of it, so leaving them in would report a mapping artefact as a price premium. Pass peer_comparable=False to see a line's own book instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>- CROSS-SECTION, not a series: one collection date, sailings read across horizons. It assumes sailings at different horizons are otherwise comparable, hence one region and no suites or packages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>- median_pppn is the median ACROSS SAILINGS, each sailing first reduced to its own median cabin, so a big ship counts once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>- dispersion_pct = (p75-p25)/median across sailings. Uniform pricing across a season is what un-optimised revenue management looks like.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>- sold_out_share is the cross-line depletion measure. closed_share is WITHIN-LINE ONLY: Carnival publishes no 'limited' state, so a closed share would read structurally higher for NCL regardless of demand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>- bands never straddle 120 days, NCLH's stated final-payment boundary; edges are [0, 15, 30, 45, 60, 75, 90, 105, 120, 135, 150, 180, 210, 240, 270, 365, 450, 540, 730].</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>- premium_vs_peer_pct compares medians inside the same band, so it is not contaminated by the two lines deploying at different horizons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>- CONFOUND: a band is a horizon, not a season. Days-to-departure is mechanically tied to sail date, so 365-539 days out is a different part of the calendar from 120-149 and carries a different fleet and itinerary mix. `sail_from`, `sail_to` and `median_nights` expose that mix per row. Read the LEVEL of the premium far out versus near in; do not read band-to-band wiggles as the curve moving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>- promo_share is NULL, not 0, for a line that publishes no offer detail. Carnival is such a line: its blank is a source gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>- SPLIT BY SAIL PERIOD IS NEARLY COLLINEAR WITH HORIZON: on one collection date a 2028 sailing can only be far out and a near-term sailing can only be 2026. Compare years only inside a dtd_band both occupy, and note that even there the calendar months differ. Holding horizon AND season fixed at once needs two collection dates a year apart, which is what the panel accumulates toward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>- Categories compared are inside / oceanview / balcony. Suites are excluded by default because the two lines' suite tiers are not the same product, and so is NCL's MINISUITE for the same reason.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>- LENGTH IS HELD FIXED: rows are also split by itinerary-length band, and the premium is computed inside one. Per-night price is not comparable across lengths, and the two lines deploy different lengths at the same horizon. Pass by_nights=False to pool lengths, which prices the deployment mix as well as the fare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>dtd_band</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>nights_band</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>sailings</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>priced_sailings</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>cells</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>median_pppn</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>p25_pppn</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>p75_pppn</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>dispersion_pct</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>sold_out_share</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>closed_share_within_line</t>
+        </is>
+      </c>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>promo_share</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>bookable_cells</t>
+        </is>
+      </c>
+      <c r="P22" s="5" t="inlineStr">
+        <is>
+          <t>sail_from</t>
+        </is>
+      </c>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>sail_to</t>
+        </is>
+      </c>
+      <c r="R22" s="5" t="inlineStr">
+        <is>
+          <t>median_nights</t>
+        </is>
+      </c>
+      <c r="S22" s="5" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="T22" s="5" t="inlineStr">
+        <is>
+          <t>premium_vs_peer_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 30-44</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>7-8n</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>8</v>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>114.14</v>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>102.71</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>125.57</v>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="L23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O23" t="n">
+        <v>6</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
+        <v>7</v>
+      </c>
+      <c r="S23" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (sailings=2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 45-59</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>7-8n</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>7</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>112</v>
+      </c>
+      <c r="I24" s="8" t="n">
+        <v>95.56999999999999</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>128.43</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="L24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="6" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="O24" t="n">
+        <v>6</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>2026-11-14</t>
+        </is>
+      </c>
+      <c r="R24" t="n">
+        <v>7</v>
+      </c>
+      <c r="S24" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (sailings=2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 60-74</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>7-8n</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>118.43</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>118.43</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>118.43</v>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2026-11-21</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2026-11-21</t>
+        </is>
+      </c>
+      <c r="R25" t="n">
+        <v>7</v>
+      </c>
+      <c r="S25" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (sailings=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 30-44</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>7-8n</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>111.29</v>
+      </c>
+      <c r="I26" s="8" t="n">
+        <v>111.29</v>
+      </c>
+      <c r="J26" s="8" t="n">
+        <v>111.29</v>
+      </c>
+      <c r="K26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
+        <v>7</v>
+      </c>
+      <c r="S26" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (sailings=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 45-59</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>7-8n</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4</v>
+      </c>
+      <c r="G27" t="n">
+        <v>16</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>112.71</v>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>109.86</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>129.86</v>
+      </c>
+      <c r="K27" s="6" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="L27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O27" t="n">
+        <v>12</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>7</v>
+      </c>
+      <c r="S27" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (sailings=4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 60-74</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>7-8n</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4</v>
+      </c>
+      <c r="G28" t="n">
+        <v>16</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>121.29</v>
+      </c>
+      <c r="I28" s="8" t="n">
+        <v>112.71</v>
+      </c>
+      <c r="J28" s="8" t="n">
+        <v>162.71</v>
+      </c>
+      <c r="K28" s="6" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="L28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O28" t="n">
+        <v>12</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2026-11-21</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>2026-11-29</t>
+        </is>
+      </c>
+      <c r="R28" t="n">
+        <v>7</v>
+      </c>
+      <c r="S28" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (sailings=4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 75-89</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>7-8n</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4</v>
+      </c>
+      <c r="G29" t="n">
+        <v>16</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>117.71</v>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>112.71</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>129.86</v>
+      </c>
+      <c r="K29" s="6" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="L29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O29" t="n">
+        <v>12</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2026-12-05</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>2026-12-13</t>
+        </is>
+      </c>
+      <c r="R29" t="n">
+        <v>7</v>
+      </c>
+      <c r="S29" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (sailings=4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 90-104</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>7-8n</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4</v>
+      </c>
+      <c r="G30" t="n">
+        <v>16</v>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>228.43</v>
+      </c>
+      <c r="I30" s="8" t="n">
+        <v>201.29</v>
+      </c>
+      <c r="J30" s="8" t="n">
+        <v>351.29</v>
+      </c>
+      <c r="K30" s="6" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="L30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O30" t="n">
+        <v>12</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2026-12-19</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>2026-12-27</t>
+        </is>
+      </c>
+      <c r="R30" t="n">
+        <v>7</v>
+      </c>
+      <c r="S30" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (sailings=4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 15-29</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Southern Europe</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>7-8n</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>153.12</v>
+      </c>
+      <c r="I31" s="8" t="n">
+        <v>153.12</v>
+      </c>
+      <c r="J31" s="8" t="n">
+        <v>153.12</v>
+      </c>
+      <c r="K31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="R31" t="n">
+        <v>8</v>
+      </c>
+      <c r="S31" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (sailings=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 15-29</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Southern Europe</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>7-8n</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>17</v>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>179.86</v>
+      </c>
+      <c r="I32" s="8" t="n">
+        <v>175.57</v>
+      </c>
+      <c r="J32" s="8" t="n">
+        <v>192</v>
+      </c>
+      <c r="K32" s="6" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="L32" s="6" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="N32" s="6" t="n">
+        <v>0.6471</v>
+      </c>
+      <c r="O32" t="n">
+        <v>13</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="R32" t="n">
+        <v>7</v>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>THIN (sailings=5)</t>
+        </is>
+      </c>
+      <c r="T32" s="6" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 30-44</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Southern Europe</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>7-8n</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>17</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>165.57</v>
+      </c>
+      <c r="I33" s="8" t="n">
+        <v>164.14</v>
+      </c>
+      <c r="J33" s="8" t="n">
+        <v>182</v>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="L33" s="6" t="n">
+        <v>0.1333</v>
+      </c>
+      <c r="M33" s="6" t="n">
+        <v>0.1333</v>
+      </c>
+      <c r="N33" s="6" t="n">
+        <v>0.7647</v>
+      </c>
+      <c r="O33" t="n">
+        <v>15</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="R33" t="n">
+        <v>7</v>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>THIN (sailings=5)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A22:T33"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
+    <col width="27" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Final payment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Do fares and sold-out share jump as sailings cross final payment? A cutoff SCAN, so the boundary is located rather than assumed. Check peer_own_jump_pct before reading any row: where the control jumps too, the cutoff has caught the calendar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Time scope: this scrape date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>[daily-marker] sail 2026-10-31..2026-12-27 | regions: Caribbean | observed 2026-09-17 | 68 obs / 17 sailings | granularity: category</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>! daily-marker is the Oct-Dec 2026 near-term cohort, and its region mix is set by seasonal deployment, not by sampling choice. Measured from the near-term universe on 2026-09-15: Caribbean 104 eligible itineraries (85 NCL / 19 Carnival); Southern Europe 15, ALL NCL, all departing October-early November, 0 in December and 0 on Carnival; Alaska 0. So cross-line work in this tier is Caribbean-only, and its Southern Europe rows are a single-line October series that dies when the Mediterranean season ends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>! COVERAGE: no Southern Europe rows in this tier. Southern Europe evidence must come from weekly-full and be reported separately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>! SINGLE-REGION BASIS: every row here is Caribbean. Do not generalise this to the other regions in the panel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>! CUTOFF SCAN: several candidate boundaries are reported so the break can be located rather than assumed. Reading only the row that suits the argument is p-hacking; report the profile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>- Windows are [C-30, C) inside final payment and [C, C+30) outside it, on days to departure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>- price_jump_pct is inside minus outside: a line that discounts once the money is committed reads NEGATIVE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>- did_* subtract the peer's own jump at the same cutoff. That is the control, and it only works while the peer's OWN final-payment boundary lies outside both windows -- peer_own_jump_pct is there to be checked, not decoration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>- SEASONALITY IS THE BINDING CONSTRAINT. On a single collection date days-to-departure is a one-to-one map onto the calendar, so the two windows are always different weeks of the year. Where a cutoff puts the holiday peak on one side, BOTH lines jump and the discontinuity is the calendar, not final payment. `inside_sails` / `outside_sails` and `peer_own_jump_pct` are there to catch exactly that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>- A discontinuity on one collection date is suggestive. The same sailings observed weekly AS they cross the boundary is the stronger test, and the panel accumulates toward it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>cutoff_days</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>n_inside</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>n_outside</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>inside_sails</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>outside_sails</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>median_inside</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>median_outside</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>price_jump_pct</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>sold_out_inside</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>sold_out_outside</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>sold_out_jump_pp</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>promo_inside</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>promo_outside</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>peer_own_jump_pct</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="inlineStr">
+        <is>
+          <t>did_price_pct</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>did_sold_out_pp</t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-31..2026-10-31</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>111.29</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R17" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="R18" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>30</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-31..2026-11-15</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>111.29</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R19" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>30</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="R20" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>45</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-10-31..2026-10-31</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-11-07..2026-11-29</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>111.29</v>
+      </c>
+      <c r="H21" t="n">
+        <v>114.14</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R21" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>45</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="R22" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>60</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-10-31..2026-11-15</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-11-21..2026-12-13</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>111.29</v>
+      </c>
+      <c r="H23" t="n">
+        <v>117.71</v>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R23" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>60</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="R24" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>75</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-11-07..2026-11-29</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-12-05..2026-12-27</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>114.14</v>
+      </c>
+      <c r="H25" t="n">
+        <v>147.71</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>-22.7</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R25" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>75</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="R26" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>90</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>8</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-11-21..2026-12-13</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-12-19..2026-12-27</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>117.71</v>
+      </c>
+      <c r="H27" t="n">
+        <v>228.43</v>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>-48.5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R27" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>90</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="R28" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>105</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-12-05..2026-12-27</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>147.71</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R29" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>105</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="R30" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-12-19..2026-12-27</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>228.43</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R31" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="R32" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="R33" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="R34" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>150</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="R35" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>150</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="R36" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>165</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="R37" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>165</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="R38" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>180</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="R39" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>180</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="R40" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>195</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="R41" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>195</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="R42" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>210</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="R43" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>210</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>None..None</t>
+        </is>
+      </c>
+      <c r="R44" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (min side=0)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A16:R44"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3054,117 +6775,90 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>- gap_pct &gt; 0 means the treatment line prices above the peer set.</t>
+          <t>- Dropped from the category comparison as not peer-comparable: MINISUITE. A tier only one line files under a shared category would otherwise read as that line pricing higher.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>- `sample` grades the smaller side of each row: THIN below 30 cells, VERY THIN below 10. It is a per-row column, not a footnote, so it travels with the number.</t>
+          <t>- gap_pct &gt; 0 means the treatment line prices above the peer set.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>- `sample` grades the smaller side of each row: THIN below 30 cells, VERY THIN below 10. It is a per-row column, not a footnote, so it travels with the number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>- `pkg_excluded_t` / `pkg_excluded_pct_t` are the treatment rows the cruise-only filter removed from that cell. A high percentage means the surviving sample is a different product mix from the region's headline row count.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>treatment_n</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>peer_n</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>treatment_median_pppn</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>peer_median_pppn</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>gap_pppn</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>gap_pct</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>pkg_excluded_t</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>pkg_excluded_pct_t</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>sample</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>status</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Bermuda</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>balcony</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>9</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (n=1 &lt; 5)</t>
-        </is>
-      </c>
-      <c r="L18" s="10" t="inlineStr">
-        <is>
-          <t>insufficient cells (need &gt;= 5 each side)</t>
         </is>
       </c>
     </row>
@@ -3176,7 +6870,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>inside</t>
+          <t>balcony</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3210,14 +6904,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>oceanview</t>
+          <t>inside</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -3227,7 +6921,7 @@
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>INSUFFICIENT (n=0 &lt; 5)</t>
+          <t>INSUFFICIENT (n=1 &lt; 5)</t>
         </is>
       </c>
       <c r="L20" s="10" t="inlineStr">
@@ -3244,14 +6938,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>suite</t>
+          <t>oceanview</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -3261,7 +6955,7 @@
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>INSUFFICIENT (n=1 &lt; 5)</t>
+          <t>INSUFFICIENT (n=0 &lt; 5)</t>
         </is>
       </c>
       <c r="L21" s="10" t="inlineStr">
@@ -3273,31 +6967,19 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Bermuda</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>balcony</t>
+          <t>suite</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>84</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>192.71</v>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>159.12</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>33.59</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>21.11</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -3305,14 +6987,14 @@
       <c r="J22" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (n=1 &lt; 5)</t>
+        </is>
+      </c>
+      <c r="L22" s="10" t="inlineStr">
+        <is>
+          <t>insufficient cells (need &gt;= 5 each side)</t>
         </is>
       </c>
     </row>
@@ -3324,26 +7006,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>inside</t>
+          <t>balcony</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>17</v>
       </c>
       <c r="D23" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>101.29</v>
+        <v>148.43</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>103.67</v>
+        <v>159.12</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>-2.38</v>
+        <v>-10.7</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-2.3</v>
+        <v>-6.72</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -3370,26 +7052,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>oceanview</t>
+          <t>inside</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>17</v>
       </c>
       <c r="D24" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>122.71</v>
+        <v>101.29</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>117.33</v>
+        <v>103.67</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>5.38</v>
+        <v>-2.38</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>4.59</v>
+        <v>-2.3</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -3416,26 +7098,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>suite</t>
+          <t>oceanview</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D25" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>508.43</v>
+        <v>122.71</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>255.2</v>
+        <v>117.33</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>253.23</v>
+        <v>5.38</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>99.23</v>
+        <v>4.59</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -3443,9 +7125,9 @@
       <c r="J25" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>THIN (n=17)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3457,19 +7139,31 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>balcony</t>
+          <t>suite</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>67</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>508.43</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>255.2</v>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>253.23</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>99.23</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -3477,14 +7171,14 @@
       <c r="J26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K26" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (n=0 &lt; 5)</t>
-        </is>
-      </c>
-      <c r="L26" s="10" t="inlineStr">
-        <is>
-          <t>insufficient cells (need &gt;= 5 each side)</t>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -3496,7 +7190,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>inside</t>
+          <t>balcony</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3530,7 +7224,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>oceanview</t>
+          <t>inside</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3564,11 +7258,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>suite</t>
+          <t>oceanview</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -3593,19 +7287,19 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Northern Europe</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>balcony</t>
+          <t>suite</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -3615,7 +7309,7 @@
       </c>
       <c r="K30" s="9" t="inlineStr">
         <is>
-          <t>INSUFFICIENT (n=1 &lt; 5)</t>
+          <t>INSUFFICIENT (n=0 &lt; 5)</t>
         </is>
       </c>
       <c r="L30" s="10" t="inlineStr">
@@ -3632,11 +7326,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>inside</t>
+          <t>balcony</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D31" t="n">
         <v>1</v>
@@ -3666,11 +7360,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>oceanview</t>
+          <t>inside</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D32" t="n">
         <v>1</v>
@@ -3700,39 +7394,73 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>oceanview</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>7</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (n=1 &lt; 5)</t>
+        </is>
+      </c>
+      <c r="L33" s="10" t="inlineStr">
+        <is>
+          <t>insufficient cells (need &gt;= 5 each side)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Southern Europe</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>suite</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C34" t="n">
         <v>18</v>
       </c>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="9" t="inlineStr">
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
         <is>
           <t>INSUFFICIENT (n=1 &lt; 5)</t>
         </is>
       </c>
-      <c r="L33" s="10" t="inlineStr">
+      <c r="L34" s="10" t="inlineStr">
         <is>
           <t>insufficient cells (need &gt;= 5 each side)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A17:L33"/>
+  <autoFilter ref="A18:L34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4766,7 +8494,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12136,7 +15864,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14213,7 +17941,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17974,1368 +21702,4 @@
   <autoFilter ref="A15:R63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="46" customWidth="1" min="9" max="9"/>
-    <col width="35" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="46" customWidth="1" min="17" max="17"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Promo reference</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>The decoder ring: every offer observed, in the vendor's own words, with its reach and scope. Read the Promo diff against this rather than against a hash.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Time scope: reference (every date in the tier).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>[daily-marker] sail 2026-10-01..2026-12-31 | regions: Bermuda, Caribbean, Northern Europe, Southern Europe | observed 2026-09-16..2026-09-17 | 1152 obs / 146 sailings | granularity: category</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>! daily-marker is the Oct-Dec 2026 near-term cohort, and its region mix is set by seasonal deployment, not by sampling choice. Measured from the near-term universe on 2026-09-15: Caribbean 104 eligible itineraries (85 NCL / 19 Carnival); Southern Europe 15, ALL NCL, all departing October-early November, 0 in December and 0 on Carnival; Alaska 0. So cross-line work in this tier is Caribbean-only, and its Southern Europe rows are a single-line October series that dies when the Mediterranean season ends.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>! PEER-COMPARABLE REGIONS in this basis: Bermuda, Caribbean, Southern Europe. Single-line only (no peer rows, so no cross-line claim can rest on them): Northern Europe (Norwegian Cruise Line).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>! NOT ALL LINES PUBLISH OFFERS: Carnival Cruise Line, Royal Caribbean International expose no promo detail at all, so their absence from this table is a gap in the source, not evidence that they are not discounting. Any cross-line read on promotion intensity is one-sided.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>- One row per (line, offer code). A promo_hash is a bundle of offers, so one bundle contributes to several rows; `bundles` counts how many distinct bundles carried this offer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>- share_of_line_cells is out of ALL that line's cells in scope, priced or not, so it reads as reach across the book.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>- `inclusion` = Mandatory means the vendor applies it automatically; it is a headline fare condition, not an opt-in the shopper chose.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>- Text is the vendor's own, verbatim from the archived payload.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>line</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>code</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>inclusion</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>offer_type</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>featured</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>cells</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>share_of_line_cells</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>regions</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>cabin_categories</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>n_ships</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>bundles</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>first_scrape</t>
-        </is>
-      </c>
-      <c r="N14" s="5" t="inlineStr">
-        <is>
-          <t>last_scrape</t>
-        </is>
-      </c>
-      <c r="O14" s="5" t="inlineStr">
-        <is>
-          <t>sail_from</t>
-        </is>
-      </c>
-      <c r="P14" s="5" t="inlineStr">
-        <is>
-          <t>sail_to</t>
-        </is>
-      </c>
-      <c r="Q14" s="5" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>50-off-all-cruises-offer</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>50% Off All Cruises</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>auto-included-offer</t>
-        </is>
-      </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>442</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>0.8185</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Bermuda, Caribbean, Northern Europe, Southern Europe</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>balcony, inside, oceanview, suite</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>11</v>
-      </c>
-      <c r="L15" t="n">
-        <v>10</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2026-12-30</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Save big with 50% off cruise fares for all guests.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>travel-protection-norwegiancare</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Travel Protection | NorwegianCare</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>travel-protection-offer</t>
-        </is>
-      </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>442</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>0.8185</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Bermuda, Caribbean, Northern Europe, Southern Europe</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>balcony, inside, oceanview, suite</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>11</v>
-      </c>
-      <c r="L16" t="n">
-        <v>10</v>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2026-12-30</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Travel
-Protection can help with unforeseen circumstances and get your trip covered
-from shore to ship.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>travel-protection-essentials</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Travel Protection | Essentials</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>travel-protection-offer</t>
-        </is>
-      </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>442</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>0.8185</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Bermuda, Caribbean, Northern Europe, Southern Europe</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>balcony, inside, oceanview, suite</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>11</v>
-      </c>
-      <c r="L17" t="n">
-        <v>10</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2026-12-30</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Travel Protection | Essentials</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>prepaid-service-charges</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Prepaid Service Charges</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>prepaid-service-charge-offer</t>
-        </is>
-      </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>442</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>0.8185</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Bermuda, Caribbean, Northern Europe, Southern Europe</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>balcony, inside, oceanview, suite</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>11</v>
-      </c>
-      <c r="L18" t="n">
-        <v>10</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2026-12-30</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Prepaying gratuities can provide peace of mind for a smoother cruise experience.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>50-pct-Off-All-Cruises-Offer</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>50% Off All Cruises</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>stateroom-offer</t>
-        </is>
-      </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>442</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>0.8185</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Bermuda, Caribbean, Northern Europe, Southern Europe</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>balcony, inside, oceanview, suite</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>11</v>
-      </c>
-      <c r="L19" t="n">
-        <v>10</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2026-12-30</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Save big with 50% off cruise fares for all guests.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>unlimited-open-bar-offer</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Bar</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Removable</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>beverage-package-offer</t>
-        </is>
-      </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>442</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>0.8185</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Bermuda, Caribbean, Northern Europe, Southern Europe</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>balcony, inside, oceanview, suite</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>11</v>
-      </c>
-      <c r="L20" t="n">
-        <v>10</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2026-12-30</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Enjoy the best beverage package at sea! Indulge in unlimited
-premium spirits such as Grey Goose, Casamigos, Woodford Reserve and more, plus
-cocktails, wine, beer, soft drinks and juice — all included. Simply pay the
-package gratuities in advance, and the drinks are on us. With drinks on board
-averaging $15 each, there’s no better value.&lt;/p&gt;&lt;p&gt;Gratuities are $32 per person, per day for 2–5 night
-sailings and $28.50 per person, per day for sailings of 6 nights or more. This
-is reflected in the total price shown above and in the guest breakdown.&lt;br&gt;&lt;/p&gt;&lt;p&gt;The package applies to all guests in the stateroom aged 21+.
-Guests 1 or 2 under age 21 will instead receive juice and unlimited fountain
-soda for $12.50 per person per day. Guests 3–8 under 21 will not receive a
-beverage package but may purchase one separately.&lt;/p&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>specialty-dining-offer</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Dining</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Removable</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>dining-offer</t>
-        </is>
-      </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>442</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>0.8185</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Bermuda, Caribbean, Northern Europe, Southern Europe</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>balcony, inside, oceanview, suite</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>11</v>
-      </c>
-      <c r="L21" t="n">
-        <v>10</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2026-12-30</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Savor amazing multi-course meals at our award-winning Specialty Restaurants, such as Cagney’s Steakhouse or Le Bistro. Enjoy elevated dining experiences featuring globally inspired cuisine and exceptional service — all included. Simply pre-pay the package gratuities in advance, and the dining experience is on us. With an average of $60 per meal onboard, this value can’t be beat. &lt;br&gt;  &lt;br&gt;   The package applies to all guests on the reservation.  Guests under age 13 dine for free when ordering from the kids’ menu. If they choose to order from the specialty dining menu, a $20 cover charge will apply.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>free-wifi-offer</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Wi-Fi Package</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>wifi-package-offer</t>
-        </is>
-      </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>442</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>0.8185</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Bermuda, Caribbean, Northern Europe, Southern Europe</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>balcony, inside, oceanview, suite</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>11</v>
-      </c>
-      <c r="L22" t="n">
-        <v>10</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2026-12-30</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Stay connected throughout your cruise with 150 minutes of hi-speed Wi-Fi per person included. Offer applies to all guests in the stateroom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>excursion-credits-offer</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Excursion Credits</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>shorex-offer</t>
-        </is>
-      </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>442</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>0.8185</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Bermuda, Caribbean, Northern Europe, Southern Europe</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>balcony, inside, oceanview, suite</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>11</v>
-      </c>
-      <c r="L23" t="n">
-        <v>10</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2026-12-30</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Receive a $50 credit toward every shore excursion. Offer applies to the first guest on the reservation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>specialty-dining-offer-7-8-nights</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Dining</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Removable</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>dining-offer</t>
-        </is>
-      </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>379</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>0.7019</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Bermuda, Caribbean, Southern Europe</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>balcony, inside, oceanview, suite</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>8</v>
-      </c>
-      <c r="L24" t="n">
-        <v>5</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2026-12-30</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Savor 3 amazing multi-course meals at our award-winning Specialty Restaurants, such as Cagney’s Steakhouse or Le Bistro. Enjoy elevated dining experiences featuring globally inspired cuisine and exceptional service — all included. Simply pre-pay the package gratuities in advance, and the dining experience is on us. With an average of $60 per meal onboard, this value can’t be beat. &lt;br&gt;  &lt;br&gt;  The package applies to all guests on the reservation.  Guests under age 13 dine for free when ordering from the kids’ menu. If they choose to order from the specialty dining menu, a $20 cover charge will apply.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Kids-Sail-Free-Offer</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Kids Sail Free</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>auto-included-offer</t>
-        </is>
-      </c>
-      <c r="F25" t="b">
-        <v>1</v>
-      </c>
-      <c r="G25" t="n">
-        <v>280</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>0.5185</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Bermuda, Caribbean, Southern Europe</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>balcony, inside, oceanview, suite</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>9</v>
-      </c>
-      <c r="L25" t="n">
-        <v>5</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>3rd &amp; 4th guests in the same stateroom pay only taxes, and fees.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Past-Guest-Offer</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Past Guest Offer</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>auto-included-offer</t>
-        </is>
-      </c>
-      <c r="F26" t="b">
-        <v>1</v>
-      </c>
-      <c r="G26" t="n">
-        <v>64</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>0.1185</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Bermuda, Caribbean, Southern Europe</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>balcony, inside, oceanview, suite</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>6</v>
-      </c>
-      <c r="L26" t="n">
-        <v>4</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>Extra Latitudes Point</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>specialty-dining-offer-9-nights</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Dining</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Removable</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>dining-offer</t>
-        </is>
-      </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>47</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Northern Europe, Southern Europe</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>balcony, inside, oceanview, suite</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>3</v>
-      </c>
-      <c r="L27" t="n">
-        <v>2</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>Savor 4 amazing multi-course meals at our award-winning Specialty Restaurants, such as Cagney’s Steakhouse or Le Bistro. Enjoy elevated dining experiences featuring globally inspired cuisine and exceptional service — all included. Simply pre-pay the package gratuities in advance, and the dining experience is on us. With an average of $60 per meal onboard, this value can’t be beat.&lt;br&gt;   &lt;br&gt;    The package applies to all guests on the reservation.  Guests under age 13 dine for free when ordering from the kids’ menu. If they choose to order from the specialty dining menu, a $20 cover charge will apply.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>specialty-dining-offer-5-6-nights</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Dining</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Removable</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>dining-offer</t>
-        </is>
-      </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>16</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>0.0296</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Bermuda, Caribbean</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>balcony, inside, oceanview, suite</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
-        <v>2</v>
-      </c>
-      <c r="L28" t="n">
-        <v>3</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>Savor 2 amazing multi-course meals at our award-winning Specialty Restaurants, such as Cagney’s Steakhouse or Le Bistro. Enjoy elevated dining experiences featuring globally inspired cuisine and exceptional service — all included. Simply pre-pay the package gratuities in advance, and the dining experience is on us. With an average of $60 per meal onboard, this value can’t be beat.&lt;br&gt; &lt;br&gt; The package applies to all guests on the reservation.  Guests under age 13 dine for free when ordering from the kids’ menu. If they choose to order from the specialty dining menu, a $20 cover charge will apply.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>latitudes-rewards-members-cruise</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Latitudes Annual Member Cruise</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>auto-included-offer</t>
-        </is>
-      </c>
-      <c r="F29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" t="n">
-        <v>12</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>0.0222</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Caribbean</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>balcony, inside, oceanview, suite</t>
-        </is>
-      </c>
-      <c r="K29" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>2026-12-06</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>2026-12-06</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>Latitudes Member Cruise</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A14:Q29"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/reports/2026-09-17__daily-marker.xlsx
+++ b/reports/2026-09-17__daily-marker.xlsx
@@ -10,25 +10,27 @@
     <sheet name="Index" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Availability" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Booking curve" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Final payment" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Peer gap" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Earnings window" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Cohort index" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Depletion" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Promo diff" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Promo reference" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Curve by hull gen" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Final payment" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Peer gap" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Earnings window" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cohort index" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Depletion" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Promo diff" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Promo reference" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Index'!$A$44:$G$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Index'!$A$45:$G$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Availability'!$A$15:$P$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Booking curve'!$A$22:$T$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Final payment'!$A$16:$R$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Peer gap'!$A$18:$L$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Earnings window'!$A$11:$I$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cohort index'!$A$17:$S$115</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Depletion'!$A$15:$U$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Promo diff'!$A$15:$R$63</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Promo reference'!$A$14:$Q$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Booking curve'!$A$23:$V$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Curve by hull gen'!$A$25:$V$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Final payment'!$A$16:$R$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Peer gap'!$A$18:$L$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Earnings window'!$A$11:$I$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Cohort index'!$A$17:$S$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Depletion'!$A$15:$U$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Promo diff'!$A$15:$R$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Promo reference'!$A$14:$Q$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -620,7 +622,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-17T20:11:08+00:00</t>
+          <t>2026-09-17T21:26:12+00:00</t>
         </is>
       </c>
     </row>
@@ -733,12 +735,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Final payment</t>
+          <t>Curve by hull gen</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>final-payment</t>
+          <t>curve-by-hull</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -747,7 +749,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -756,19 +758,19 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Do fares and sold-out share jump as sailings cross final payment? A cutoff SCAN, so the boundary is located rather than assumed. Check peer_own_jump_pct before reading any row: where the control jumps too, the cutoff has caught the calendar.</t>
+          <t>The same curve holding hull GENERATION fixed -- NCL's newest tonnage against Carnival's newest, not against a blend. Class names never match across lines, so generation is the comparable axis and it is mapped explicitly in config.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Peer gap</t>
+          <t>Final payment</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>peer-gap</t>
+          <t>final-payment</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -777,7 +779,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -786,19 +788,19 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>NCLH vs peer median pppn, per region and cabin category, on cruise-only rows.</t>
+          <t>Do fares and sold-out share jump as sailings cross final payment? A cutoff SCAN, so the boundary is located rather than assumed. Check peer_own_jump_pct before reading any row: where the control jumps too, the cutoff has caught the calendar.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Earnings window</t>
+          <t>Peer gap</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>earnings-window</t>
+          <t>peer-gap</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -807,7 +809,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -816,28 +818,28 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sailings departing inside the NCLH print window vs outside it. Split on sail date, not collection date.</t>
+          <t>NCLH vs peer median pppn, per region and cabin category, on cruise-only rows.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cohort index</t>
+          <t>Earnings window</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>cohort-index</t>
+          <t>earnings-window</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>all scrape dates in the tier</t>
+          <t>this scrape date</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -846,19 +848,19 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Since-inception index on a MATCHED BASKET of cabins, with the naive all-rows index beside it. index_matched cannot be moved by sailings entering the book; mix_effect_pp is how much of the naive move is composition rather than price.</t>
+          <t>Sailings departing inside the NCLH print window vs outside it. Split on sail date, not collection date.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Depletion</t>
+          <t>Cohort index</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>depletion</t>
+          <t>cohort-index</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -867,7 +869,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -876,19 +878,19 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Change in closed share per day. Needs &gt;=2 collection dates or it reports nothing rather than inventing a slope.</t>
+          <t>Since-inception index on a MATCHED BASKET of cabins, with the naive all-rows index beside it. index_matched cannot be moved by sailings entering the book; mix_effect_pp is how much of the naive move is composition rather than price.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Promo diff</t>
+          <t>Depletion</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>promo-diff</t>
+          <t>depletion</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -897,7 +899,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -906,117 +908,127 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Which offers widened, narrowed, appeared or were withdrawn between dates, by reach on cabins seen both times.</t>
+          <t>Change in closed share per day. Needs &gt;=2 collection dates or it reports nothing rather than inventing a slope.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Promo diff</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>promo-diff</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>all scrape dates in the tier</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>48</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Which offers widened, narrowed, appeared or were withdrawn between dates, by reach on cabins seen both times.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Promo reference</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>promo-reference</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>reference (every date in the tier)</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D29" t="n">
         <v>15</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>The decoder ring: every offer observed, in the vendor's own words, with its reach and scope. Read the Promo diff against this rather than against a hash.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Region coverage on this basis</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Every region the config asks for, including those that returned nothing. A region with 0 rows is absent from every sheet; without this table that is indistinguishable from a region nobody requested.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>observations</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>sailings</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>lines</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>package_rows</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Caribbean</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>467</v>
-      </c>
-      <c r="C34" t="n">
-        <v>104</v>
-      </c>
-      <c r="D34" t="n">
-        <v>2</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>79</v>
+        <v>467</v>
       </c>
       <c r="C35" t="n">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="D35" t="n">
         <v>2</v>
@@ -1029,17 +1041,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="C36" t="n">
+        <v>14</v>
+      </c>
+      <c r="D36" t="n">
         <v>2</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -1049,17 +1061,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Bermuda</t>
+          <t>Northern Europe</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -1069,136 +1081,3919 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaska</t>
+          <t>Bermuda</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>no rows on this basis -- absent from every sheet</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>Alaska</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>no rows on this basis -- absent from every sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Transatlantic</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="inlineStr">
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>no rows on this basis -- absent from every sheet</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>Scope comparability between collection dates</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Whether each pair of adjacent collection dates sampled the same population. Where `comparable` is NO, the collector itself changed, and every slope or index spanning that pair is measuring the change to the collector as well as the market.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>from_date</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>to_date</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>sailings_before</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>sailings_after</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>sailings_delta_pct</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>comparable</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>why_not</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="C45" t="n">
+      <c r="C46" t="n">
         <v>113</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D46" t="n">
         <v>126</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="E46" s="6" t="n">
         <v>11.5</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A44:G45"/>
+  <autoFilter ref="A45:G46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R63"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Promo diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Which offers widened, narrowed, appeared or were withdrawn between dates, by reach on cabins seen both times.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Time scope: all scrape dates in the tier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>[daily-marker] sail 2026-10-01..2026-12-31 | regions: Bermuda, Caribbean, Northern Europe, Southern Europe | observed 2026-09-16..2026-09-17 | 1152 obs / 146 sailings | granularity: category</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>! daily-marker is the Oct-Dec 2026 near-term cohort, and its region mix is set by seasonal deployment, not by sampling choice. Measured from the near-term universe on 2026-09-15: Caribbean 104 eligible itineraries (85 NCL / 19 Carnival); Southern Europe 15, ALL NCL, all departing October-early November, 0 in December and 0 on Carnival; Alaska 0. So cross-line work in this tier is Caribbean-only, and its Southern Europe rows are a single-line October series that dies when the Mediterranean season ends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>! PEER-COMPARABLE REGIONS in this basis: Bermuda, Caribbean, Southern Europe. Single-line only (no peer rows, so no cross-line claim can rest on them): Northern Europe (Norwegian Cruise Line).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>! ONE-SIDED: Carnival Cruise Line, Royal Caribbean International publish no offer detail, so this table can only describe NCLH's promotional behaviour. It cannot support 'NCLH is discounting harder than the peer' -- the peer's discounting is not observable here at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>- COMMON SUPPORT: shares are the fraction of cabins observed on BOTH dates that carried the offer. Sailings entering the book cannot move them, so a widened collection scope cannot read as a promo change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>- naive_* is share of everything each date returned; mix_effect_pp is how many points of the naive move are composition rather than offer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>- Reach, not count: an offer on one ship and an offer fleet-wide are both 'one promo', and the difference is the whole signal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>- status: NEW / WITHDRAWN are appearance and disappearance on matched cabins; widened and narrowed are reach moves beyond 2 points.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>- A promotion that deepens without widening does not show here: this measures reach, not discount depth. Depth is in the fare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>from_date</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>to_date</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>inclusion</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>matched_cells</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>cells_before</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>cells_after</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>share_before</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>share_after</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>delta_share_pp</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>naive_share_before</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="inlineStr">
+        <is>
+          <t>naive_share_after</t>
+        </is>
+      </c>
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>mix_effect_pp</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>50-off-all-cruises-offer</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>50% Off All Cruises</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" t="n">
+        <v>26</v>
+      </c>
+      <c r="J16" t="n">
+        <v>25</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="L16" s="6" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="M16" s="6" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>narrowed</t>
+        </is>
+      </c>
+      <c r="O16" s="6" t="n">
+        <v>0.7297</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="R16" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>50-pct-Off-All-Cruises-Offer</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>50% Off All Cruises</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" t="n">
+        <v>26</v>
+      </c>
+      <c r="J17" t="n">
+        <v>25</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="L17" s="6" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>narrowed</t>
+        </is>
+      </c>
+      <c r="O17" s="6" t="n">
+        <v>0.7297</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="R17" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Kids-Sail-Free-Offer</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kids Sail Free</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" t="n">
+        <v>20</v>
+      </c>
+      <c r="J18" t="n">
+        <v>19</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="L18" s="6" t="n">
+        <v>0.6333</v>
+      </c>
+      <c r="M18" s="6" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>narrowed</t>
+        </is>
+      </c>
+      <c r="O18" s="6" t="n">
+        <v>0.5676</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v>0.6333</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="R18" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Past-Guest-Offer</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Past Guest Offer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" t="n">
+        <v>16</v>
+      </c>
+      <c r="J19" t="n">
+        <v>16</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>0.5333</v>
+      </c>
+      <c r="L19" s="6" t="n">
+        <v>0.5333</v>
+      </c>
+      <c r="M19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="O19" s="6" t="n">
+        <v>0.4324</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v>0.5333</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="R19" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>excursion-credits-offer</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Excursion Credits</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" t="n">
+        <v>26</v>
+      </c>
+      <c r="J20" t="n">
+        <v>25</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="L20" s="6" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>narrowed</t>
+        </is>
+      </c>
+      <c r="O20" s="6" t="n">
+        <v>0.7297</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="R20" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>free-wifi-offer</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Wi-Fi Package</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" t="n">
+        <v>26</v>
+      </c>
+      <c r="J21" t="n">
+        <v>25</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="L21" s="6" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="M21" s="6" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>narrowed</t>
+        </is>
+      </c>
+      <c r="O21" s="6" t="n">
+        <v>0.7297</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="R21" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>prepaid-service-charges</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Prepaid Service Charges</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" t="n">
+        <v>26</v>
+      </c>
+      <c r="J22" t="n">
+        <v>25</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="L22" s="6" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>narrowed</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="n">
+        <v>0.7297</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="R22" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>specialty-dining-offer</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Dining</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" t="n">
+        <v>26</v>
+      </c>
+      <c r="J23" t="n">
+        <v>25</v>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="L23" s="6" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="M23" s="6" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>narrowed</t>
+        </is>
+      </c>
+      <c r="O23" s="6" t="n">
+        <v>0.7297</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="R23" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>specialty-dining-offer-7-8-nights</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dining</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" t="n">
+        <v>26</v>
+      </c>
+      <c r="J24" t="n">
+        <v>25</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="L24" s="6" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>narrowed</t>
+        </is>
+      </c>
+      <c r="O24" s="6" t="n">
+        <v>0.7027</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="R24" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>travel-protection-essentials</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Travel Protection | Essentials</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" t="n">
+        <v>26</v>
+      </c>
+      <c r="J25" t="n">
+        <v>25</v>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="L25" s="6" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="M25" s="6" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>narrowed</t>
+        </is>
+      </c>
+      <c r="O25" s="6" t="n">
+        <v>0.7297</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="R25" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>travel-protection-norwegiancare</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Travel Protection | NorwegianCare</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" t="n">
+        <v>26</v>
+      </c>
+      <c r="J26" t="n">
+        <v>25</v>
+      </c>
+      <c r="K26" s="6" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="L26" s="6" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>narrowed</t>
+        </is>
+      </c>
+      <c r="O26" s="6" t="n">
+        <v>0.7297</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="R26" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>unlimited-open-bar-offer</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Bar</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" t="n">
+        <v>26</v>
+      </c>
+      <c r="J27" t="n">
+        <v>25</v>
+      </c>
+      <c r="K27" s="6" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="L27" s="6" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>narrowed</t>
+        </is>
+      </c>
+      <c r="O27" s="6" t="n">
+        <v>0.7297</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="R27" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>50-off-all-cruises-offer</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>50% Off All Cruises</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>119</v>
+      </c>
+      <c r="I28" t="n">
+        <v>98</v>
+      </c>
+      <c r="J28" t="n">
+        <v>98</v>
+      </c>
+      <c r="K28" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="L28" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="O28" s="6" t="n">
+        <v>0.8268</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="R28" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=119)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>50-pct-Off-All-Cruises-Offer</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>50% Off All Cruises</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>119</v>
+      </c>
+      <c r="I29" t="n">
+        <v>98</v>
+      </c>
+      <c r="J29" t="n">
+        <v>98</v>
+      </c>
+      <c r="K29" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="L29" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="M29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="n">
+        <v>0.8268</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="R29" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=119)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Kids-Sail-Free-Offer</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Kids Sail Free</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>119</v>
+      </c>
+      <c r="I30" t="n">
+        <v>63</v>
+      </c>
+      <c r="J30" t="n">
+        <v>63</v>
+      </c>
+      <c r="K30" s="6" t="n">
+        <v>0.5294</v>
+      </c>
+      <c r="L30" s="6" t="n">
+        <v>0.5294</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="O30" s="6" t="n">
+        <v>0.4637</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v>0.5294</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="R30" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=119)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Past-Guest-Offer</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Past Guest Offer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>119</v>
+      </c>
+      <c r="I31" t="n">
+        <v>6</v>
+      </c>
+      <c r="J31" t="n">
+        <v>6</v>
+      </c>
+      <c r="K31" s="6" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="L31" s="6" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="M31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="O31" s="6" t="n">
+        <v>0.08939999999999999</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="R31" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=119)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>excursion-credits-offer</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Excursion Credits</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>119</v>
+      </c>
+      <c r="I32" t="n">
+        <v>98</v>
+      </c>
+      <c r="J32" t="n">
+        <v>98</v>
+      </c>
+      <c r="K32" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="L32" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="O32" s="6" t="n">
+        <v>0.8268</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="R32" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=119)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>free-wifi-offer</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Wi-Fi Package</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>119</v>
+      </c>
+      <c r="I33" t="n">
+        <v>98</v>
+      </c>
+      <c r="J33" t="n">
+        <v>98</v>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="L33" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="M33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="O33" s="6" t="n">
+        <v>0.8268</v>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="R33" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=119)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>latitudes-rewards-members-cruise</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Latitudes Annual Member Cruise</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>119</v>
+      </c>
+      <c r="I34" t="n">
+        <v>6</v>
+      </c>
+      <c r="J34" t="n">
+        <v>6</v>
+      </c>
+      <c r="K34" s="6" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="L34" s="6" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="O34" s="6" t="n">
+        <v>0.0335</v>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R34" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=119)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>prepaid-service-charges</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Prepaid Service Charges</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>119</v>
+      </c>
+      <c r="I35" t="n">
+        <v>98</v>
+      </c>
+      <c r="J35" t="n">
+        <v>98</v>
+      </c>
+      <c r="K35" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="L35" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="M35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="O35" s="6" t="n">
+        <v>0.8268</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="R35" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=119)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>specialty-dining-offer</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Dining</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>119</v>
+      </c>
+      <c r="I36" t="n">
+        <v>98</v>
+      </c>
+      <c r="J36" t="n">
+        <v>98</v>
+      </c>
+      <c r="K36" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="L36" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="M36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="O36" s="6" t="n">
+        <v>0.8268</v>
+      </c>
+      <c r="P36" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="R36" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=119)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>specialty-dining-offer-7-8-nights</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Dining</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>119</v>
+      </c>
+      <c r="I37" t="n">
+        <v>98</v>
+      </c>
+      <c r="J37" t="n">
+        <v>98</v>
+      </c>
+      <c r="K37" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="L37" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="M37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="O37" s="6" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="R37" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=119)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>travel-protection-essentials</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Travel Protection | Essentials</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>119</v>
+      </c>
+      <c r="I38" t="n">
+        <v>98</v>
+      </c>
+      <c r="J38" t="n">
+        <v>98</v>
+      </c>
+      <c r="K38" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="L38" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="M38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="O38" s="6" t="n">
+        <v>0.8268</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="R38" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=119)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>travel-protection-norwegiancare</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Travel Protection | NorwegianCare</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>119</v>
+      </c>
+      <c r="I39" t="n">
+        <v>98</v>
+      </c>
+      <c r="J39" t="n">
+        <v>98</v>
+      </c>
+      <c r="K39" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="L39" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="M39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="O39" s="6" t="n">
+        <v>0.8268</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="R39" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=119)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>unlimited-open-bar-offer</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Bar</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>119</v>
+      </c>
+      <c r="I40" t="n">
+        <v>98</v>
+      </c>
+      <c r="J40" t="n">
+        <v>98</v>
+      </c>
+      <c r="K40" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="L40" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="M40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="O40" s="6" t="n">
+        <v>0.8268</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="R40" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=119)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Northern Europe</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>50-off-all-cruises-offer</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>50% Off All Cruises</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>10</v>
+      </c>
+      <c r="I41" t="n">
+        <v>8</v>
+      </c>
+      <c r="J41" t="n">
+        <v>9</v>
+      </c>
+      <c r="K41" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L41" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M41" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>widened</t>
+        </is>
+      </c>
+      <c r="O41" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="10" t="inlineStr">
+        <is>
+          <t>THIN (n=10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Northern Europe</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>50-pct-Off-All-Cruises-Offer</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>50% Off All Cruises</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>10</v>
+      </c>
+      <c r="I42" t="n">
+        <v>8</v>
+      </c>
+      <c r="J42" t="n">
+        <v>9</v>
+      </c>
+      <c r="K42" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L42" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M42" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>widened</t>
+        </is>
+      </c>
+      <c r="O42" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="10" t="inlineStr">
+        <is>
+          <t>THIN (n=10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Northern Europe</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>excursion-credits-offer</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Excursion Credits</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>10</v>
+      </c>
+      <c r="I43" t="n">
+        <v>8</v>
+      </c>
+      <c r="J43" t="n">
+        <v>9</v>
+      </c>
+      <c r="K43" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L43" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M43" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>widened</t>
+        </is>
+      </c>
+      <c r="O43" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="10" t="inlineStr">
+        <is>
+          <t>THIN (n=10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Northern Europe</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>free-wifi-offer</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Wi-Fi Package</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>10</v>
+      </c>
+      <c r="I44" t="n">
+        <v>8</v>
+      </c>
+      <c r="J44" t="n">
+        <v>9</v>
+      </c>
+      <c r="K44" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L44" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M44" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>widened</t>
+        </is>
+      </c>
+      <c r="O44" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="10" t="inlineStr">
+        <is>
+          <t>THIN (n=10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Northern Europe</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>prepaid-service-charges</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Prepaid Service Charges</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I45" t="n">
+        <v>8</v>
+      </c>
+      <c r="J45" t="n">
+        <v>9</v>
+      </c>
+      <c r="K45" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L45" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M45" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>widened</t>
+        </is>
+      </c>
+      <c r="O45" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="10" t="inlineStr">
+        <is>
+          <t>THIN (n=10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Northern Europe</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>specialty-dining-offer</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Dining</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>10</v>
+      </c>
+      <c r="I46" t="n">
+        <v>8</v>
+      </c>
+      <c r="J46" t="n">
+        <v>9</v>
+      </c>
+      <c r="K46" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L46" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M46" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>widened</t>
+        </is>
+      </c>
+      <c r="O46" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="10" t="inlineStr">
+        <is>
+          <t>THIN (n=10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Northern Europe</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>specialty-dining-offer-9-nights</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Dining</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>10</v>
+      </c>
+      <c r="I47" t="n">
+        <v>8</v>
+      </c>
+      <c r="J47" t="n">
+        <v>9</v>
+      </c>
+      <c r="K47" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L47" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M47" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>widened</t>
+        </is>
+      </c>
+      <c r="O47" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="10" t="inlineStr">
+        <is>
+          <t>THIN (n=10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Northern Europe</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>travel-protection-essentials</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Travel Protection | Essentials</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>10</v>
+      </c>
+      <c r="I48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J48" t="n">
+        <v>9</v>
+      </c>
+      <c r="K48" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L48" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M48" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>widened</t>
+        </is>
+      </c>
+      <c r="O48" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="10" t="inlineStr">
+        <is>
+          <t>THIN (n=10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Northern Europe</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>travel-protection-norwegiancare</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Travel Protection | NorwegianCare</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>10</v>
+      </c>
+      <c r="I49" t="n">
+        <v>8</v>
+      </c>
+      <c r="J49" t="n">
+        <v>9</v>
+      </c>
+      <c r="K49" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L49" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M49" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>widened</t>
+        </is>
+      </c>
+      <c r="O49" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="10" t="inlineStr">
+        <is>
+          <t>THIN (n=10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Northern Europe</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>unlimited-open-bar-offer</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Bar</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>10</v>
+      </c>
+      <c r="I50" t="n">
+        <v>8</v>
+      </c>
+      <c r="J50" t="n">
+        <v>9</v>
+      </c>
+      <c r="K50" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L50" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M50" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>widened</t>
+        </is>
+      </c>
+      <c r="O50" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="10" t="inlineStr">
+        <is>
+          <t>THIN (n=10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Southern Europe</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>50-off-all-cruises-offer</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>50% Off All Cruises</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>69</v>
+      </c>
+      <c r="I51" t="n">
+        <v>56</v>
+      </c>
+      <c r="J51" t="n">
+        <v>57</v>
+      </c>
+      <c r="K51" s="6" t="n">
+        <v>0.8116</v>
+      </c>
+      <c r="L51" s="6" t="n">
+        <v>0.8260999999999999</v>
+      </c>
+      <c r="M51" s="6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="O51" s="6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v>0.8267</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="R51" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=69)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Southern Europe</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>50-pct-Off-All-Cruises-Offer</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>50% Off All Cruises</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>69</v>
+      </c>
+      <c r="I52" t="n">
+        <v>56</v>
+      </c>
+      <c r="J52" t="n">
+        <v>57</v>
+      </c>
+      <c r="K52" s="6" t="n">
+        <v>0.8116</v>
+      </c>
+      <c r="L52" s="6" t="n">
+        <v>0.8260999999999999</v>
+      </c>
+      <c r="M52" s="6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="O52" s="6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v>0.8267</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="R52" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=69)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Southern Europe</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Kids-Sail-Free-Offer</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Kids Sail Free</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>69</v>
+      </c>
+      <c r="I53" t="n">
+        <v>39</v>
+      </c>
+      <c r="J53" t="n">
+        <v>41</v>
+      </c>
+      <c r="K53" s="6" t="n">
+        <v>0.5652</v>
+      </c>
+      <c r="L53" s="6" t="n">
+        <v>0.5942</v>
+      </c>
+      <c r="M53" s="6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>widened</t>
+        </is>
+      </c>
+      <c r="O53" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v>0.6133</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="R53" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=69)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Southern Europe</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Past-Guest-Offer</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Past Guest Offer</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>69</v>
+      </c>
+      <c r="I54" t="n">
+        <v>5</v>
+      </c>
+      <c r="J54" t="n">
+        <v>5</v>
+      </c>
+      <c r="K54" s="6" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="L54" s="6" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="M54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="O54" s="6" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v>0.0667</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="R54" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=69)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Southern Europe</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>excursion-credits-offer</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Excursion Credits</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>69</v>
+      </c>
+      <c r="I55" t="n">
+        <v>56</v>
+      </c>
+      <c r="J55" t="n">
+        <v>57</v>
+      </c>
+      <c r="K55" s="6" t="n">
+        <v>0.8116</v>
+      </c>
+      <c r="L55" s="6" t="n">
+        <v>0.8260999999999999</v>
+      </c>
+      <c r="M55" s="6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="O55" s="6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v>0.8267</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="R55" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=69)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Southern Europe</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>free-wifi-offer</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Wi-Fi Package</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>69</v>
+      </c>
+      <c r="I56" t="n">
+        <v>56</v>
+      </c>
+      <c r="J56" t="n">
+        <v>57</v>
+      </c>
+      <c r="K56" s="6" t="n">
+        <v>0.8116</v>
+      </c>
+      <c r="L56" s="6" t="n">
+        <v>0.8260999999999999</v>
+      </c>
+      <c r="M56" s="6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="O56" s="6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v>0.8267</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="R56" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=69)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Southern Europe</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>prepaid-service-charges</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Prepaid Service Charges</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>69</v>
+      </c>
+      <c r="I57" t="n">
+        <v>56</v>
+      </c>
+      <c r="J57" t="n">
+        <v>57</v>
+      </c>
+      <c r="K57" s="6" t="n">
+        <v>0.8116</v>
+      </c>
+      <c r="L57" s="6" t="n">
+        <v>0.8260999999999999</v>
+      </c>
+      <c r="M57" s="6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="O57" s="6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v>0.8267</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="R57" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=69)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Southern Europe</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>specialty-dining-offer</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Dining</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>69</v>
+      </c>
+      <c r="I58" t="n">
+        <v>56</v>
+      </c>
+      <c r="J58" t="n">
+        <v>57</v>
+      </c>
+      <c r="K58" s="6" t="n">
+        <v>0.8116</v>
+      </c>
+      <c r="L58" s="6" t="n">
+        <v>0.8260999999999999</v>
+      </c>
+      <c r="M58" s="6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="O58" s="6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v>0.8267</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="R58" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=69)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Southern Europe</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>specialty-dining-offer-7-8-nights</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Dining</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>69</v>
+      </c>
+      <c r="I59" t="n">
+        <v>41</v>
+      </c>
+      <c r="J59" t="n">
+        <v>42</v>
+      </c>
+      <c r="K59" s="6" t="n">
+        <v>0.5942</v>
+      </c>
+      <c r="L59" s="6" t="n">
+        <v>0.6087</v>
+      </c>
+      <c r="M59" s="6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="O59" s="6" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="P59" s="6" t="n">
+        <v>0.6267</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="R59" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=69)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Southern Europe</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>specialty-dining-offer-9-nights</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Dining</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>69</v>
+      </c>
+      <c r="I60" t="n">
+        <v>15</v>
+      </c>
+      <c r="J60" t="n">
+        <v>15</v>
+      </c>
+      <c r="K60" s="6" t="n">
+        <v>0.2174</v>
+      </c>
+      <c r="L60" s="6" t="n">
+        <v>0.2174</v>
+      </c>
+      <c r="M60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="O60" s="6" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R60" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=69)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Southern Europe</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>travel-protection-essentials</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Travel Protection | Essentials</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>69</v>
+      </c>
+      <c r="I61" t="n">
+        <v>56</v>
+      </c>
+      <c r="J61" t="n">
+        <v>57</v>
+      </c>
+      <c r="K61" s="6" t="n">
+        <v>0.8116</v>
+      </c>
+      <c r="L61" s="6" t="n">
+        <v>0.8260999999999999</v>
+      </c>
+      <c r="M61" s="6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="O61" s="6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v>0.8267</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="R61" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=69)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Southern Europe</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>travel-protection-norwegiancare</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Travel Protection | NorwegianCare</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>69</v>
+      </c>
+      <c r="I62" t="n">
+        <v>56</v>
+      </c>
+      <c r="J62" t="n">
+        <v>57</v>
+      </c>
+      <c r="K62" s="6" t="n">
+        <v>0.8116</v>
+      </c>
+      <c r="L62" s="6" t="n">
+        <v>0.8260999999999999</v>
+      </c>
+      <c r="M62" s="6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="O62" s="6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v>0.8267</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="R62" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=69)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Southern Europe</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>unlimited-open-bar-offer</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Bar</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>69</v>
+      </c>
+      <c r="I63" t="n">
+        <v>56</v>
+      </c>
+      <c r="J63" t="n">
+        <v>57</v>
+      </c>
+      <c r="K63" s="6" t="n">
+        <v>0.8116</v>
+      </c>
+      <c r="L63" s="6" t="n">
+        <v>0.8260999999999999</v>
+      </c>
+      <c r="M63" s="6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="O63" s="6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v>0.8267</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="R63" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=69)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A15:R63"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4385,7 +8180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T33"/>
+  <dimension ref="A1:V34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4408,6 +8203,8 @@
     <col width="15" customWidth="1" min="18" max="18"/>
     <col width="27" customWidth="1" min="19" max="19"/>
     <col width="21" customWidth="1" min="20" max="20"/>
+    <col width="17" customWidth="1" min="21" max="21"/>
+    <col width="23" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4504,217 +8301,161 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>- premium_vs_peer_pct compares medians inside the same band, so it is not contaminated by the two lines deploying at different horizons.</t>
+          <t>- index_vs_own_far_band rebases each line to its own median in a base band COMMON to every line in the cell (100 = that band). It answers the bundle objection: inclusions shift a line's LEVEL, not the shape of its own decline, so a line falling against itself is discounting whatever is in the fare. index_base_band names the band each row is indexed to -- rows with different bases are not comparable to each other.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>- CONFOUND: a band is a horizon, not a season. Days-to-departure is mechanically tied to sail date, so 365-539 days out is a different part of the calendar from 120-149 and carries a different fleet and itinerary mix. `sail_from`, `sail_to` and `median_nights` expose that mix per row. Read the LEVEL of the premium far out versus near in; do not read band-to-band wiggles as the curve moving.</t>
+          <t>- premium_vs_peer_pct compares medians inside the same band, so it is not contaminated by the two lines deploying at different horizons.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>- promo_share is NULL, not 0, for a line that publishes no offer detail. Carnival is such a line: its blank is a source gap.</t>
+          <t>- CONFOUND: a band is a horizon, not a season. Days-to-departure is mechanically tied to sail date, so 365-539 days out is a different part of the calendar from 120-149 and carries a different fleet and itinerary mix. `sail_from`, `sail_to` and `median_nights` expose that mix per row. Read the LEVEL of the premium far out versus near in; do not read band-to-band wiggles as the curve moving.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>- SPLIT BY SAIL PERIOD IS NEARLY COLLINEAR WITH HORIZON: on one collection date a 2028 sailing can only be far out and a near-term sailing can only be 2026. Compare years only inside a dtd_band both occupy, and note that even there the calendar months differ. Holding horizon AND season fixed at once needs two collection dates a year apart, which is what the panel accumulates toward.</t>
+          <t>- promo_share is NULL, not 0, for a line that publishes no offer detail. Carnival is such a line: its blank is a source gap.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>- Categories compared are inside / oceanview / balcony. Suites are excluded by default because the two lines' suite tiers are not the same product, and so is NCL's MINISUITE for the same reason.</t>
+          <t>- SPLIT BY SAIL PERIOD IS NEARLY COLLINEAR WITH HORIZON: on one collection date a 2028 sailing can only be far out and a near-term sailing can only be 2026. Compare years only inside a dtd_band both occupy, and note that even there the calendar months differ. Holding horizon AND season fixed at once needs two collection dates a year apart, which is what the panel accumulates toward.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>- Categories compared are inside / oceanview / balcony. Suites are excluded by default because the two lines' suite tiers are not the same product, and so is NCL's MINISUITE for the same reason.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
           <t>- LENGTH IS HELD FIXED: rows are also split by itinerary-length band, and the premium is computed inside one. Per-night price is not comparable across lengths, and the two lines deploy different lengths at the same horizon. Pass by_nights=False to pool lengths, which prices the deployment mix as well as the fare.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>line</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>dtd_band</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>nights_band</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>sailings</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>priced_sailings</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>cells</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>median_pppn</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>p25_pppn</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>p75_pppn</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>dispersion_pct</t>
         </is>
       </c>
-      <c r="L22" s="5" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>sold_out_share</t>
         </is>
       </c>
-      <c r="M22" s="5" t="inlineStr">
+      <c r="M23" s="5" t="inlineStr">
         <is>
           <t>closed_share_within_line</t>
         </is>
       </c>
-      <c r="N22" s="5" t="inlineStr">
+      <c r="N23" s="5" t="inlineStr">
         <is>
           <t>promo_share</t>
         </is>
       </c>
-      <c r="O22" s="5" t="inlineStr">
+      <c r="O23" s="5" t="inlineStr">
         <is>
           <t>bookable_cells</t>
         </is>
       </c>
-      <c r="P22" s="5" t="inlineStr">
+      <c r="P23" s="5" t="inlineStr">
         <is>
           <t>sail_from</t>
         </is>
       </c>
-      <c r="Q22" s="5" t="inlineStr">
+      <c r="Q23" s="5" t="inlineStr">
         <is>
           <t>sail_to</t>
         </is>
       </c>
-      <c r="R22" s="5" t="inlineStr">
+      <c r="R23" s="5" t="inlineStr">
         <is>
           <t>median_nights</t>
         </is>
       </c>
-      <c r="S22" s="5" t="inlineStr">
+      <c r="S23" s="5" t="inlineStr">
         <is>
           <t>sample</t>
         </is>
       </c>
-      <c r="T22" s="5" t="inlineStr">
+      <c r="T23" s="5" t="inlineStr">
         <is>
           <t>premium_vs_peer_pct</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 30-44</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Bermuda</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>7-8n</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>2</v>
-      </c>
-      <c r="F23" t="n">
-        <v>2</v>
-      </c>
-      <c r="G23" t="n">
-        <v>8</v>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>114.14</v>
-      </c>
-      <c r="I23" s="8" t="n">
-        <v>102.71</v>
-      </c>
-      <c r="J23" s="8" t="n">
-        <v>125.57</v>
-      </c>
-      <c r="K23" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="L23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="6" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O23" t="n">
-        <v>6</v>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="R23" t="n">
-        <v>7</v>
-      </c>
-      <c r="S23" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (sailings=2)</t>
+      <c r="U23" s="5" t="inlineStr">
+        <is>
+          <t>index_base_band</t>
+        </is>
+      </c>
+      <c r="V23" s="5" t="inlineStr">
+        <is>
+          <t>index_vs_own_far_band</t>
         </is>
       </c>
     </row>
@@ -4726,7 +8467,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 45-59</t>
+          <t xml:space="preserve"> 30-44</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4746,19 +8487,19 @@
         <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>112</v>
+        <v>114.14</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>95.56999999999999</v>
+        <v>102.71</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>128.43</v>
+        <v>125.57</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>29.3</v>
+        <v>20</v>
       </c>
       <c r="L24" s="6" t="n">
         <v>0</v>
@@ -4767,19 +8508,19 @@
         <v>0</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.8571</v>
+        <v>0.75</v>
       </c>
       <c r="O24" t="n">
         <v>6</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="R24" t="n">
@@ -4799,7 +8540,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 60-74</t>
+          <t xml:space="preserve"> 45-59</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4813,25 +8554,25 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>118.43</v>
+        <v>112</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>118.43</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>118.43</v>
+        <v>128.43</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0</v>
+        <v>29.3</v>
       </c>
       <c r="L25" s="6" t="n">
         <v>0</v>
@@ -4840,19 +8581,19 @@
         <v>0</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>1</v>
+        <v>0.8571</v>
       </c>
       <c r="O25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R25" t="n">
@@ -4860,7 +8601,7 @@
       </c>
       <c r="S25" s="9" t="inlineStr">
         <is>
-          <t>INSUFFICIENT (sailings=1)</t>
+          <t>INSUFFICIENT (sailings=2)</t>
         </is>
       </c>
     </row>
@@ -4872,12 +8613,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 30-44</t>
+          <t xml:space="preserve"> 60-74</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Bermuda</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4892,16 +8633,16 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>111.29</v>
+        <v>118.43</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>111.29</v>
+        <v>118.43</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>111.29</v>
+        <v>118.43</v>
       </c>
       <c r="K26" s="6" t="n">
         <v>0</v>
@@ -4913,19 +8654,19 @@
         <v>0</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="R26" t="n">
@@ -4945,7 +8686,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 45-59</t>
+          <t xml:space="preserve"> 30-44</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4959,25 +8700,25 @@
         </is>
       </c>
       <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
         <v>4</v>
       </c>
-      <c r="F27" t="n">
-        <v>4</v>
-      </c>
-      <c r="G27" t="n">
-        <v>16</v>
-      </c>
       <c r="H27" s="8" t="n">
-        <v>112.71</v>
+        <v>111.29</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>109.86</v>
+        <v>111.29</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>129.86</v>
+        <v>111.29</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>17.7</v>
+        <v>0</v>
       </c>
       <c r="L27" s="6" t="n">
         <v>0</v>
@@ -4989,16 +8730,16 @@
         <v>0.75</v>
       </c>
       <c r="O27" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="R27" t="n">
@@ -5006,7 +8747,7 @@
       </c>
       <c r="S27" s="9" t="inlineStr">
         <is>
-          <t>INSUFFICIENT (sailings=4)</t>
+          <t>INSUFFICIENT (sailings=1)</t>
         </is>
       </c>
     </row>
@@ -5018,7 +8759,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 60-74</t>
+          <t xml:space="preserve"> 45-59</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -5041,16 +8782,16 @@
         <v>16</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>121.29</v>
+        <v>112.71</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>112.71</v>
+        <v>109.86</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>162.71</v>
+        <v>129.86</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>41.2</v>
+        <v>17.7</v>
       </c>
       <c r="L28" s="6" t="n">
         <v>0</v>
@@ -5066,12 +8807,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R28" t="n">
@@ -5091,7 +8832,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 75-89</t>
+          <t xml:space="preserve"> 60-74</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5114,16 +8855,16 @@
         <v>16</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>117.71</v>
+        <v>121.29</v>
       </c>
       <c r="I29" s="8" t="n">
         <v>112.71</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>129.86</v>
+        <v>162.71</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>14.6</v>
+        <v>41.2</v>
       </c>
       <c r="L29" s="6" t="n">
         <v>0</v>
@@ -5139,12 +8880,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="R29" t="n">
@@ -5164,7 +8905,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 90-104</t>
+          <t xml:space="preserve"> 75-89</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5187,16 +8928,16 @@
         <v>16</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>228.43</v>
+        <v>117.71</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>201.29</v>
+        <v>112.71</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>351.29</v>
+        <v>129.86</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>65.7</v>
+        <v>14.6</v>
       </c>
       <c r="L30" s="6" t="n">
         <v>0</v>
@@ -5212,12 +8953,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R30" t="n">
@@ -5232,17 +8973,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Carnival Cruise Line</t>
+          <t>Norwegian Cruise Line</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 15-29</t>
+          <t xml:space="preserve"> 90-104</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5251,25 +8992,25 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>153.12</v>
+        <v>228.43</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>153.12</v>
+        <v>201.29</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>153.12</v>
+        <v>351.29</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0</v>
+        <v>65.7</v>
       </c>
       <c r="L31" s="6" t="n">
         <v>0</v>
@@ -5277,32 +9018,35 @@
       <c r="M31" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="N31" s="6" t="n">
+        <v>0.75</v>
+      </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S31" s="9" t="inlineStr">
         <is>
-          <t>INSUFFICIENT (sailings=1)</t>
+          <t>INSUFFICIENT (sailings=4)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Norwegian Cruise Line</t>
+          <t>Carnival Cruise Line</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5321,58 +9065,52 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>179.86</v>
+        <v>153.12</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>175.57</v>
+        <v>153.12</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>192</v>
+        <v>153.12</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.1538</v>
+        <v>0</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.1538</v>
-      </c>
-      <c r="N32" s="6" t="n">
-        <v>0.6471</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="R32" t="n">
-        <v>7</v>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>THIN (sailings=5)</t>
-        </is>
-      </c>
-      <c r="T32" s="6" t="n">
-        <v>17.5</v>
+        <v>8</v>
+      </c>
+      <c r="S32" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (sailings=1)</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -5383,7 +9121,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 30-44</t>
+          <t xml:space="preserve"> 15-29</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5406,37 +9144,37 @@
         <v>17</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>165.57</v>
+        <v>179.86</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>164.14</v>
+        <v>175.57</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>10.8</v>
+        <v>9.1</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.1333</v>
+        <v>0.1538</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.1333</v>
+        <v>0.1538</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.7647</v>
+        <v>0.6471</v>
       </c>
       <c r="O33" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="R33" t="n">
@@ -5447,14 +9185,776 @@
           <t>THIN (sailings=5)</t>
         </is>
       </c>
+      <c r="T33" s="6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 30-44</t>
+        </is>
+      </c>
+      <c r="V33" s="6" t="n">
+        <v>108.6</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 30-44</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Southern Europe</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>7-8n</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>17</v>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>165.57</v>
+      </c>
+      <c r="I34" s="8" t="n">
+        <v>164.14</v>
+      </c>
+      <c r="J34" s="8" t="n">
+        <v>182</v>
+      </c>
+      <c r="K34" s="6" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="L34" s="6" t="n">
+        <v>0.1333</v>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>0.1333</v>
+      </c>
+      <c r="N34" s="6" t="n">
+        <v>0.7647</v>
+      </c>
+      <c r="O34" t="n">
+        <v>15</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="R34" t="n">
+        <v>7</v>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>THIN (sailings=5)</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 30-44</t>
+        </is>
+      </c>
+      <c r="V34" s="6" t="n">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A22:T33"/>
+  <autoFilter ref="A23:V34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="27" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="20" max="20"/>
+    <col width="17" customWidth="1" min="21" max="21"/>
+    <col width="23" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Curve by hull gen</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>The same curve holding hull GENERATION fixed -- NCL's newest tonnage against Carnival's newest, not against a blend. Class names never match across lines, so generation is the comparable axis and it is mapped explicitly in config.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Time scope: this scrape date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>[daily-marker] sail 2026-10-31..2026-12-27 | regions: Caribbean | observed 2026-09-17 | 68 obs / 17 sailings | granularity: category</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>! daily-marker is the Oct-Dec 2026 near-term cohort, and its region mix is set by seasonal deployment, not by sampling choice. Measured from the near-term universe on 2026-09-15: Caribbean 104 eligible itineraries (85 NCL / 19 Carnival); Southern Europe 15, ALL NCL, all departing October-early November, 0 in December and 0 on Carnival; Alaska 0. So cross-line work in this tier is Caribbean-only, and its Southern Europe rows are a single-line October series that dies when the Mediterranean season ends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>! COVERAGE: no Southern Europe rows in this tier. Southern Europe evidence must come from weekly-full and be reported separately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>! SINGLE-REGION BASIS: every row here is Caribbean. Do not generalise this to the other regions in the panel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>! PRODUCT FILTER: cruise-only. Of 419 priced rows in scope, 419 are cruise-only, 0 are land+cruise packages (excluded), 0 are unclassified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>! PEER-COMPARABLE CABINS ONLY: dropped MINISUITE. These are filed under a peer category but are not the same product as the peer's version of it, so leaving them in would report a mapping artefact as a price premium. Pass peer_comparable=False to see a line's own book instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>! NO PEER OVERLAP: no band holds both Norwegian Cruise Line and Carnival Cruise Line, so no premium can be computed. The level column is still readable within each line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>- CROSS-SECTION, not a series: one collection date, sailings read across horizons. It assumes sailings at different horizons are otherwise comparable, hence one region and no suites or packages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>- median_pppn is the median ACROSS SAILINGS, each sailing first reduced to its own median cabin, so a big ship counts once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>- dispersion_pct = (p75-p25)/median across sailings. Uniform pricing across a season is what un-optimised revenue management looks like.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>- sold_out_share is the cross-line depletion measure. closed_share is WITHIN-LINE ONLY: Carnival publishes no 'limited' state, so a closed share would read structurally higher for NCL regardless of demand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>- bands never straddle 120 days, NCLH's stated final-payment boundary; edges are [0, 15, 30, 45, 60, 75, 90, 105, 120, 135, 150, 180, 210, 240, 270, 365, 450, 540, 730].</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>- index_vs_own_far_band rebases each line to its own median in a base band COMMON to every line in the cell (100 = that band). It answers the bundle objection: inclusions shift a line's LEVEL, not the shape of its own decline, so a line falling against itself is discounting whatever is in the fare. index_base_band names the band each row is indexed to -- rows with different bases are not comparable to each other.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>- premium_vs_peer_pct compares medians inside the same band, so it is not contaminated by the two lines deploying at different horizons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>- CONFOUND: a band is a horizon, not a season. Days-to-departure is mechanically tied to sail date, so 365-539 days out is a different part of the calendar from 120-149 and carries a different fleet and itinerary mix. `sail_from`, `sail_to` and `median_nights` expose that mix per row. Read the LEVEL of the premium far out versus near in; do not read band-to-band wiggles as the curve moving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>- promo_share is NULL, not 0, for a line that publishes no offer detail. Carnival is such a line: its blank is a source gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>- SPLIT BY SAIL PERIOD IS NEARLY COLLINEAR WITH HORIZON: on one collection date a 2028 sailing can only be far out and a near-term sailing can only be 2026. Compare years only inside a dtd_band both occupy, and note that even there the calendar months differ. Holding horizon AND season fixed at once needs two collection dates a year apart, which is what the panel accumulates toward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>- Categories compared are inside / oceanview / balcony. Suites are excluded by default because the two lines' suite tiers are not the same product, and so is NCL's MINISUITE for the same reason.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>- LENGTH IS HELD FIXED: rows are also split by itinerary-length band, and the premium is computed inside one. Per-night price is not comparable across lengths, and the two lines deploy different lengths at the same horizon. Pass by_nights=False to pool lengths, which prices the deployment mix as well as the fare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>dtd_band</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>ship_generation</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>nights_band</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>sailings</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>priced_sailings</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>cells</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>median_pppn</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>p25_pppn</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>p75_pppn</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>dispersion_pct</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>sold_out_share</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>closed_share_within_line</t>
+        </is>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>promo_share</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>bookable_cells</t>
+        </is>
+      </c>
+      <c r="P25" s="5" t="inlineStr">
+        <is>
+          <t>sail_from</t>
+        </is>
+      </c>
+      <c r="Q25" s="5" t="inlineStr">
+        <is>
+          <t>sail_to</t>
+        </is>
+      </c>
+      <c r="R25" s="5" t="inlineStr">
+        <is>
+          <t>median_nights</t>
+        </is>
+      </c>
+      <c r="S25" s="5" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="T25" s="5" t="inlineStr">
+        <is>
+          <t>premium_vs_peer_pct</t>
+        </is>
+      </c>
+      <c r="U25" s="5" t="inlineStr">
+        <is>
+          <t>index_base_band</t>
+        </is>
+      </c>
+      <c r="V25" s="5" t="inlineStr">
+        <is>
+          <t>index_vs_own_far_band</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 30-44</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>newest</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>7-8n</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>111.29</v>
+      </c>
+      <c r="I26" s="8" t="n">
+        <v>111.29</v>
+      </c>
+      <c r="J26" s="8" t="n">
+        <v>111.29</v>
+      </c>
+      <c r="K26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
+        <v>7</v>
+      </c>
+      <c r="S26" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (sailings=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 45-59</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>newest</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>7-8n</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4</v>
+      </c>
+      <c r="G27" t="n">
+        <v>16</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>112.71</v>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>109.86</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>129.86</v>
+      </c>
+      <c r="K27" s="6" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="L27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O27" t="n">
+        <v>12</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>7</v>
+      </c>
+      <c r="S27" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (sailings=4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 60-74</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>newest</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>7-8n</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4</v>
+      </c>
+      <c r="G28" t="n">
+        <v>16</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>121.29</v>
+      </c>
+      <c r="I28" s="8" t="n">
+        <v>112.71</v>
+      </c>
+      <c r="J28" s="8" t="n">
+        <v>162.71</v>
+      </c>
+      <c r="K28" s="6" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="L28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O28" t="n">
+        <v>12</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2026-11-21</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>2026-11-29</t>
+        </is>
+      </c>
+      <c r="R28" t="n">
+        <v>7</v>
+      </c>
+      <c r="S28" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (sailings=4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 75-89</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>newest</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>7-8n</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4</v>
+      </c>
+      <c r="G29" t="n">
+        <v>16</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>117.71</v>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>112.71</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>129.86</v>
+      </c>
+      <c r="K29" s="6" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="L29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O29" t="n">
+        <v>12</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2026-12-05</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>2026-12-13</t>
+        </is>
+      </c>
+      <c r="R29" t="n">
+        <v>7</v>
+      </c>
+      <c r="S29" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (sailings=4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 90-104</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>newest</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>7-8n</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4</v>
+      </c>
+      <c r="G30" t="n">
+        <v>16</v>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>228.43</v>
+      </c>
+      <c r="I30" s="8" t="n">
+        <v>201.29</v>
+      </c>
+      <c r="J30" s="8" t="n">
+        <v>351.29</v>
+      </c>
+      <c r="K30" s="6" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="L30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O30" t="n">
+        <v>12</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2026-12-19</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>2026-12-27</t>
+        </is>
+      </c>
+      <c r="R30" t="n">
+        <v>7</v>
+      </c>
+      <c r="S30" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (sailings=4)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A25:V30"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6672,7 +11172,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7460,7 +11960,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8494,7 +12994,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15864,7 +20364,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17939,3767 +22439,4 @@
   <autoFilter ref="A15:U39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:R63"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Promo diff</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Which offers widened, narrowed, appeared or were withdrawn between dates, by reach on cabins seen both times.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Time scope: all scrape dates in the tier.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>[daily-marker] sail 2026-10-01..2026-12-31 | regions: Bermuda, Caribbean, Northern Europe, Southern Europe | observed 2026-09-16..2026-09-17 | 1152 obs / 146 sailings | granularity: category</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>! daily-marker is the Oct-Dec 2026 near-term cohort, and its region mix is set by seasonal deployment, not by sampling choice. Measured from the near-term universe on 2026-09-15: Caribbean 104 eligible itineraries (85 NCL / 19 Carnival); Southern Europe 15, ALL NCL, all departing October-early November, 0 in December and 0 on Carnival; Alaska 0. So cross-line work in this tier is Caribbean-only, and its Southern Europe rows are a single-line October series that dies when the Mediterranean season ends.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>! PEER-COMPARABLE REGIONS in this basis: Bermuda, Caribbean, Southern Europe. Single-line only (no peer rows, so no cross-line claim can rest on them): Northern Europe (Norwegian Cruise Line).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>! ONE-SIDED: Carnival Cruise Line, Royal Caribbean International publish no offer detail, so this table can only describe NCLH's promotional behaviour. It cannot support 'NCLH is discounting harder than the peer' -- the peer's discounting is not observable here at all.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>- COMMON SUPPORT: shares are the fraction of cabins observed on BOTH dates that carried the offer. Sailings entering the book cannot move them, so a widened collection scope cannot read as a promo change.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>- naive_* is share of everything each date returned; mix_effect_pp is how many points of the naive move are composition rather than offer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>- Reach, not count: an offer on one ship and an offer fleet-wide are both 'one promo', and the difference is the whole signal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>- status: NEW / WITHDRAWN are appearance and disappearance on matched cabins; widened and narrowed are reach moves beyond 2 points.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>- A promotion that deepens without widening does not show here: this measures reach, not discount depth. Depth is in the fare.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>line</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>from_date</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>to_date</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>code</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>inclusion</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>matched_cells</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>cells_before</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>cells_after</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>share_before</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>share_after</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>delta_share_pp</t>
-        </is>
-      </c>
-      <c r="N15" s="5" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="O15" s="5" t="inlineStr">
-        <is>
-          <t>naive_share_before</t>
-        </is>
-      </c>
-      <c r="P15" s="5" t="inlineStr">
-        <is>
-          <t>naive_share_after</t>
-        </is>
-      </c>
-      <c r="Q15" s="5" t="inlineStr">
-        <is>
-          <t>mix_effect_pp</t>
-        </is>
-      </c>
-      <c r="R15" s="5" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Bermuda</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>50-off-all-cruises-offer</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>50% Off All Cruises</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>30</v>
-      </c>
-      <c r="I16" t="n">
-        <v>26</v>
-      </c>
-      <c r="J16" t="n">
-        <v>25</v>
-      </c>
-      <c r="K16" s="6" t="n">
-        <v>0.8667</v>
-      </c>
-      <c r="L16" s="6" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="M16" s="6" t="n">
-        <v>-3.33</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>narrowed</t>
-        </is>
-      </c>
-      <c r="O16" s="6" t="n">
-        <v>0.7297</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>13.69</v>
-      </c>
-      <c r="R16" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=30)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Bermuda</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>50-pct-Off-All-Cruises-Offer</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>50% Off All Cruises</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>30</v>
-      </c>
-      <c r="I17" t="n">
-        <v>26</v>
-      </c>
-      <c r="J17" t="n">
-        <v>25</v>
-      </c>
-      <c r="K17" s="6" t="n">
-        <v>0.8667</v>
-      </c>
-      <c r="L17" s="6" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="M17" s="6" t="n">
-        <v>-3.33</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>narrowed</t>
-        </is>
-      </c>
-      <c r="O17" s="6" t="n">
-        <v>0.7297</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>13.69</v>
-      </c>
-      <c r="R17" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=30)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Bermuda</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Kids-Sail-Free-Offer</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Kids Sail Free</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>30</v>
-      </c>
-      <c r="I18" t="n">
-        <v>20</v>
-      </c>
-      <c r="J18" t="n">
-        <v>19</v>
-      </c>
-      <c r="K18" s="6" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="L18" s="6" t="n">
-        <v>0.6333</v>
-      </c>
-      <c r="M18" s="6" t="n">
-        <v>-3.33</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>narrowed</t>
-        </is>
-      </c>
-      <c r="O18" s="6" t="n">
-        <v>0.5676</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v>0.6333</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>9.91</v>
-      </c>
-      <c r="R18" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=30)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Bermuda</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Past-Guest-Offer</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Past Guest Offer</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>30</v>
-      </c>
-      <c r="I19" t="n">
-        <v>16</v>
-      </c>
-      <c r="J19" t="n">
-        <v>16</v>
-      </c>
-      <c r="K19" s="6" t="n">
-        <v>0.5333</v>
-      </c>
-      <c r="L19" s="6" t="n">
-        <v>0.5333</v>
-      </c>
-      <c r="M19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>unchanged</t>
-        </is>
-      </c>
-      <c r="O19" s="6" t="n">
-        <v>0.4324</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v>0.5333</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>10.09</v>
-      </c>
-      <c r="R19" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=30)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Bermuda</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>excursion-credits-offer</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Excursion Credits</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>30</v>
-      </c>
-      <c r="I20" t="n">
-        <v>26</v>
-      </c>
-      <c r="J20" t="n">
-        <v>25</v>
-      </c>
-      <c r="K20" s="6" t="n">
-        <v>0.8667</v>
-      </c>
-      <c r="L20" s="6" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="M20" s="6" t="n">
-        <v>-3.33</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>narrowed</t>
-        </is>
-      </c>
-      <c r="O20" s="6" t="n">
-        <v>0.7297</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>13.69</v>
-      </c>
-      <c r="R20" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=30)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Bermuda</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>free-wifi-offer</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Wi-Fi Package</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>30</v>
-      </c>
-      <c r="I21" t="n">
-        <v>26</v>
-      </c>
-      <c r="J21" t="n">
-        <v>25</v>
-      </c>
-      <c r="K21" s="6" t="n">
-        <v>0.8667</v>
-      </c>
-      <c r="L21" s="6" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="M21" s="6" t="n">
-        <v>-3.33</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>narrowed</t>
-        </is>
-      </c>
-      <c r="O21" s="6" t="n">
-        <v>0.7297</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>13.69</v>
-      </c>
-      <c r="R21" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=30)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Bermuda</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>prepaid-service-charges</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Prepaid Service Charges</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>30</v>
-      </c>
-      <c r="I22" t="n">
-        <v>26</v>
-      </c>
-      <c r="J22" t="n">
-        <v>25</v>
-      </c>
-      <c r="K22" s="6" t="n">
-        <v>0.8667</v>
-      </c>
-      <c r="L22" s="6" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="M22" s="6" t="n">
-        <v>-3.33</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>narrowed</t>
-        </is>
-      </c>
-      <c r="O22" s="6" t="n">
-        <v>0.7297</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>13.69</v>
-      </c>
-      <c r="R22" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=30)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Bermuda</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>specialty-dining-offer</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Dining</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Removable</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>30</v>
-      </c>
-      <c r="I23" t="n">
-        <v>26</v>
-      </c>
-      <c r="J23" t="n">
-        <v>25</v>
-      </c>
-      <c r="K23" s="6" t="n">
-        <v>0.8667</v>
-      </c>
-      <c r="L23" s="6" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="M23" s="6" t="n">
-        <v>-3.33</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>narrowed</t>
-        </is>
-      </c>
-      <c r="O23" s="6" t="n">
-        <v>0.7297</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>13.69</v>
-      </c>
-      <c r="R23" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=30)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Bermuda</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>specialty-dining-offer-7-8-nights</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Dining</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Removable</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>30</v>
-      </c>
-      <c r="I24" t="n">
-        <v>26</v>
-      </c>
-      <c r="J24" t="n">
-        <v>25</v>
-      </c>
-      <c r="K24" s="6" t="n">
-        <v>0.8667</v>
-      </c>
-      <c r="L24" s="6" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="M24" s="6" t="n">
-        <v>-3.33</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>narrowed</t>
-        </is>
-      </c>
-      <c r="O24" s="6" t="n">
-        <v>0.7027</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="R24" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=30)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Bermuda</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>travel-protection-essentials</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Travel Protection | Essentials</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>30</v>
-      </c>
-      <c r="I25" t="n">
-        <v>26</v>
-      </c>
-      <c r="J25" t="n">
-        <v>25</v>
-      </c>
-      <c r="K25" s="6" t="n">
-        <v>0.8667</v>
-      </c>
-      <c r="L25" s="6" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="M25" s="6" t="n">
-        <v>-3.33</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>narrowed</t>
-        </is>
-      </c>
-      <c r="O25" s="6" t="n">
-        <v>0.7297</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>13.69</v>
-      </c>
-      <c r="R25" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=30)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Bermuda</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>travel-protection-norwegiancare</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Travel Protection | NorwegianCare</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>30</v>
-      </c>
-      <c r="I26" t="n">
-        <v>26</v>
-      </c>
-      <c r="J26" t="n">
-        <v>25</v>
-      </c>
-      <c r="K26" s="6" t="n">
-        <v>0.8667</v>
-      </c>
-      <c r="L26" s="6" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="M26" s="6" t="n">
-        <v>-3.33</v>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>narrowed</t>
-        </is>
-      </c>
-      <c r="O26" s="6" t="n">
-        <v>0.7297</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>13.69</v>
-      </c>
-      <c r="R26" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=30)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Bermuda</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>unlimited-open-bar-offer</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Bar</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Removable</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>30</v>
-      </c>
-      <c r="I27" t="n">
-        <v>26</v>
-      </c>
-      <c r="J27" t="n">
-        <v>25</v>
-      </c>
-      <c r="K27" s="6" t="n">
-        <v>0.8667</v>
-      </c>
-      <c r="L27" s="6" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="M27" s="6" t="n">
-        <v>-3.33</v>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>narrowed</t>
-        </is>
-      </c>
-      <c r="O27" s="6" t="n">
-        <v>0.7297</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>13.69</v>
-      </c>
-      <c r="R27" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=30)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Caribbean</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>50-off-all-cruises-offer</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>50% Off All Cruises</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>119</v>
-      </c>
-      <c r="I28" t="n">
-        <v>98</v>
-      </c>
-      <c r="J28" t="n">
-        <v>98</v>
-      </c>
-      <c r="K28" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="L28" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="M28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>unchanged</t>
-        </is>
-      </c>
-      <c r="O28" s="6" t="n">
-        <v>0.8268</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="R28" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=119)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Caribbean</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>50-pct-Off-All-Cruises-Offer</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>50% Off All Cruises</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>119</v>
-      </c>
-      <c r="I29" t="n">
-        <v>98</v>
-      </c>
-      <c r="J29" t="n">
-        <v>98</v>
-      </c>
-      <c r="K29" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="L29" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="M29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>unchanged</t>
-        </is>
-      </c>
-      <c r="O29" s="6" t="n">
-        <v>0.8268</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="R29" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=119)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Caribbean</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Kids-Sail-Free-Offer</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Kids Sail Free</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>119</v>
-      </c>
-      <c r="I30" t="n">
-        <v>63</v>
-      </c>
-      <c r="J30" t="n">
-        <v>63</v>
-      </c>
-      <c r="K30" s="6" t="n">
-        <v>0.5294</v>
-      </c>
-      <c r="L30" s="6" t="n">
-        <v>0.5294</v>
-      </c>
-      <c r="M30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>unchanged</t>
-        </is>
-      </c>
-      <c r="O30" s="6" t="n">
-        <v>0.4637</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v>0.5294</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="R30" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=119)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Caribbean</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Past-Guest-Offer</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Past Guest Offer</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>119</v>
-      </c>
-      <c r="I31" t="n">
-        <v>6</v>
-      </c>
-      <c r="J31" t="n">
-        <v>6</v>
-      </c>
-      <c r="K31" s="6" t="n">
-        <v>0.0504</v>
-      </c>
-      <c r="L31" s="6" t="n">
-        <v>0.0504</v>
-      </c>
-      <c r="M31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>unchanged</t>
-        </is>
-      </c>
-      <c r="O31" s="6" t="n">
-        <v>0.08939999999999999</v>
-      </c>
-      <c r="P31" s="6" t="n">
-        <v>0.0504</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="R31" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=119)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Caribbean</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>excursion-credits-offer</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Excursion Credits</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>119</v>
-      </c>
-      <c r="I32" t="n">
-        <v>98</v>
-      </c>
-      <c r="J32" t="n">
-        <v>98</v>
-      </c>
-      <c r="K32" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="L32" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="M32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>unchanged</t>
-        </is>
-      </c>
-      <c r="O32" s="6" t="n">
-        <v>0.8268</v>
-      </c>
-      <c r="P32" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="R32" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=119)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Caribbean</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>free-wifi-offer</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Wi-Fi Package</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>119</v>
-      </c>
-      <c r="I33" t="n">
-        <v>98</v>
-      </c>
-      <c r="J33" t="n">
-        <v>98</v>
-      </c>
-      <c r="K33" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="L33" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="M33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>unchanged</t>
-        </is>
-      </c>
-      <c r="O33" s="6" t="n">
-        <v>0.8268</v>
-      </c>
-      <c r="P33" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="R33" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=119)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Caribbean</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>latitudes-rewards-members-cruise</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Latitudes Annual Member Cruise</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>119</v>
-      </c>
-      <c r="I34" t="n">
-        <v>6</v>
-      </c>
-      <c r="J34" t="n">
-        <v>6</v>
-      </c>
-      <c r="K34" s="6" t="n">
-        <v>0.0504</v>
-      </c>
-      <c r="L34" s="6" t="n">
-        <v>0.0504</v>
-      </c>
-      <c r="M34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>unchanged</t>
-        </is>
-      </c>
-      <c r="O34" s="6" t="n">
-        <v>0.0335</v>
-      </c>
-      <c r="P34" s="6" t="n">
-        <v>0.0504</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="R34" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=119)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Caribbean</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>prepaid-service-charges</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Prepaid Service Charges</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>119</v>
-      </c>
-      <c r="I35" t="n">
-        <v>98</v>
-      </c>
-      <c r="J35" t="n">
-        <v>98</v>
-      </c>
-      <c r="K35" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="L35" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="M35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>unchanged</t>
-        </is>
-      </c>
-      <c r="O35" s="6" t="n">
-        <v>0.8268</v>
-      </c>
-      <c r="P35" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="R35" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=119)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Caribbean</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>specialty-dining-offer</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Dining</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Removable</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>119</v>
-      </c>
-      <c r="I36" t="n">
-        <v>98</v>
-      </c>
-      <c r="J36" t="n">
-        <v>98</v>
-      </c>
-      <c r="K36" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="L36" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="M36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>unchanged</t>
-        </is>
-      </c>
-      <c r="O36" s="6" t="n">
-        <v>0.8268</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="R36" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=119)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Caribbean</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>specialty-dining-offer-7-8-nights</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Dining</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Removable</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>119</v>
-      </c>
-      <c r="I37" t="n">
-        <v>98</v>
-      </c>
-      <c r="J37" t="n">
-        <v>98</v>
-      </c>
-      <c r="K37" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="L37" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="M37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>unchanged</t>
-        </is>
-      </c>
-      <c r="O37" s="6" t="n">
-        <v>0.743</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="R37" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=119)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Caribbean</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>travel-protection-essentials</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Travel Protection | Essentials</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>119</v>
-      </c>
-      <c r="I38" t="n">
-        <v>98</v>
-      </c>
-      <c r="J38" t="n">
-        <v>98</v>
-      </c>
-      <c r="K38" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="L38" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="M38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>unchanged</t>
-        </is>
-      </c>
-      <c r="O38" s="6" t="n">
-        <v>0.8268</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="R38" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=119)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Caribbean</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>travel-protection-norwegiancare</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Travel Protection | NorwegianCare</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>119</v>
-      </c>
-      <c r="I39" t="n">
-        <v>98</v>
-      </c>
-      <c r="J39" t="n">
-        <v>98</v>
-      </c>
-      <c r="K39" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="L39" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="M39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>unchanged</t>
-        </is>
-      </c>
-      <c r="O39" s="6" t="n">
-        <v>0.8268</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="R39" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=119)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Caribbean</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>unlimited-open-bar-offer</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Bar</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Removable</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>119</v>
-      </c>
-      <c r="I40" t="n">
-        <v>98</v>
-      </c>
-      <c r="J40" t="n">
-        <v>98</v>
-      </c>
-      <c r="K40" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="L40" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="M40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>unchanged</t>
-        </is>
-      </c>
-      <c r="O40" s="6" t="n">
-        <v>0.8268</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="R40" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=119)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Northern Europe</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>50-off-all-cruises-offer</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>50% Off All Cruises</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>10</v>
-      </c>
-      <c r="I41" t="n">
-        <v>8</v>
-      </c>
-      <c r="J41" t="n">
-        <v>9</v>
-      </c>
-      <c r="K41" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L41" s="6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M41" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>widened</t>
-        </is>
-      </c>
-      <c r="O41" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" s="10" t="inlineStr">
-        <is>
-          <t>THIN (n=10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Northern Europe</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>50-pct-Off-All-Cruises-Offer</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>50% Off All Cruises</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>10</v>
-      </c>
-      <c r="I42" t="n">
-        <v>8</v>
-      </c>
-      <c r="J42" t="n">
-        <v>9</v>
-      </c>
-      <c r="K42" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L42" s="6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M42" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>widened</t>
-        </is>
-      </c>
-      <c r="O42" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" s="10" t="inlineStr">
-        <is>
-          <t>THIN (n=10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Northern Europe</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>excursion-credits-offer</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Excursion Credits</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>10</v>
-      </c>
-      <c r="I43" t="n">
-        <v>8</v>
-      </c>
-      <c r="J43" t="n">
-        <v>9</v>
-      </c>
-      <c r="K43" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L43" s="6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M43" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>widened</t>
-        </is>
-      </c>
-      <c r="O43" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="10" t="inlineStr">
-        <is>
-          <t>THIN (n=10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Northern Europe</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>free-wifi-offer</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Wi-Fi Package</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>10</v>
-      </c>
-      <c r="I44" t="n">
-        <v>8</v>
-      </c>
-      <c r="J44" t="n">
-        <v>9</v>
-      </c>
-      <c r="K44" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L44" s="6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M44" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>widened</t>
-        </is>
-      </c>
-      <c r="O44" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" s="10" t="inlineStr">
-        <is>
-          <t>THIN (n=10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Northern Europe</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>prepaid-service-charges</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Prepaid Service Charges</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
-        <v>10</v>
-      </c>
-      <c r="I45" t="n">
-        <v>8</v>
-      </c>
-      <c r="J45" t="n">
-        <v>9</v>
-      </c>
-      <c r="K45" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L45" s="6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M45" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>widened</t>
-        </is>
-      </c>
-      <c r="O45" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" s="10" t="inlineStr">
-        <is>
-          <t>THIN (n=10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Northern Europe</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>specialty-dining-offer</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Dining</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Removable</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
-        <v>10</v>
-      </c>
-      <c r="I46" t="n">
-        <v>8</v>
-      </c>
-      <c r="J46" t="n">
-        <v>9</v>
-      </c>
-      <c r="K46" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L46" s="6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M46" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>widened</t>
-        </is>
-      </c>
-      <c r="O46" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="10" t="inlineStr">
-        <is>
-          <t>THIN (n=10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Northern Europe</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>specialty-dining-offer-9-nights</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Dining</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Removable</t>
-        </is>
-      </c>
-      <c r="H47" t="n">
-        <v>10</v>
-      </c>
-      <c r="I47" t="n">
-        <v>8</v>
-      </c>
-      <c r="J47" t="n">
-        <v>9</v>
-      </c>
-      <c r="K47" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L47" s="6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M47" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>widened</t>
-        </is>
-      </c>
-      <c r="O47" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" s="10" t="inlineStr">
-        <is>
-          <t>THIN (n=10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Northern Europe</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>travel-protection-essentials</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Travel Protection | Essentials</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
-        <v>10</v>
-      </c>
-      <c r="I48" t="n">
-        <v>8</v>
-      </c>
-      <c r="J48" t="n">
-        <v>9</v>
-      </c>
-      <c r="K48" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L48" s="6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M48" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>widened</t>
-        </is>
-      </c>
-      <c r="O48" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" s="10" t="inlineStr">
-        <is>
-          <t>THIN (n=10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Northern Europe</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>travel-protection-norwegiancare</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Travel Protection | NorwegianCare</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H49" t="n">
-        <v>10</v>
-      </c>
-      <c r="I49" t="n">
-        <v>8</v>
-      </c>
-      <c r="J49" t="n">
-        <v>9</v>
-      </c>
-      <c r="K49" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L49" s="6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M49" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>widened</t>
-        </is>
-      </c>
-      <c r="O49" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" s="10" t="inlineStr">
-        <is>
-          <t>THIN (n=10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Northern Europe</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>unlimited-open-bar-offer</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Bar</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Removable</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
-        <v>10</v>
-      </c>
-      <c r="I50" t="n">
-        <v>8</v>
-      </c>
-      <c r="J50" t="n">
-        <v>9</v>
-      </c>
-      <c r="K50" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L50" s="6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M50" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>widened</t>
-        </is>
-      </c>
-      <c r="O50" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" s="10" t="inlineStr">
-        <is>
-          <t>THIN (n=10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Southern Europe</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>50-off-all-cruises-offer</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>50% Off All Cruises</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
-        <v>69</v>
-      </c>
-      <c r="I51" t="n">
-        <v>56</v>
-      </c>
-      <c r="J51" t="n">
-        <v>57</v>
-      </c>
-      <c r="K51" s="6" t="n">
-        <v>0.8116</v>
-      </c>
-      <c r="L51" s="6" t="n">
-        <v>0.8260999999999999</v>
-      </c>
-      <c r="M51" s="6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>unchanged</t>
-        </is>
-      </c>
-      <c r="O51" s="6" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v>0.8267</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="R51" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=69)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Southern Europe</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>50-pct-Off-All-Cruises-Offer</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>50% Off All Cruises</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>69</v>
-      </c>
-      <c r="I52" t="n">
-        <v>56</v>
-      </c>
-      <c r="J52" t="n">
-        <v>57</v>
-      </c>
-      <c r="K52" s="6" t="n">
-        <v>0.8116</v>
-      </c>
-      <c r="L52" s="6" t="n">
-        <v>0.8260999999999999</v>
-      </c>
-      <c r="M52" s="6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>unchanged</t>
-        </is>
-      </c>
-      <c r="O52" s="6" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v>0.8267</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="R52" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=69)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Southern Europe</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Kids-Sail-Free-Offer</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Kids Sail Free</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>69</v>
-      </c>
-      <c r="I53" t="n">
-        <v>39</v>
-      </c>
-      <c r="J53" t="n">
-        <v>41</v>
-      </c>
-      <c r="K53" s="6" t="n">
-        <v>0.5652</v>
-      </c>
-      <c r="L53" s="6" t="n">
-        <v>0.5942</v>
-      </c>
-      <c r="M53" s="6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>widened</t>
-        </is>
-      </c>
-      <c r="O53" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v>0.6133</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>-1.57</v>
-      </c>
-      <c r="R53" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=69)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Southern Europe</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Past-Guest-Offer</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Past Guest Offer</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
-        <v>69</v>
-      </c>
-      <c r="I54" t="n">
-        <v>5</v>
-      </c>
-      <c r="J54" t="n">
-        <v>5</v>
-      </c>
-      <c r="K54" s="6" t="n">
-        <v>0.0725</v>
-      </c>
-      <c r="L54" s="6" t="n">
-        <v>0.0725</v>
-      </c>
-      <c r="M54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>unchanged</t>
-        </is>
-      </c>
-      <c r="O54" s="6" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v>0.0667</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="R54" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=69)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Southern Europe</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>excursion-credits-offer</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Excursion Credits</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H55" t="n">
-        <v>69</v>
-      </c>
-      <c r="I55" t="n">
-        <v>56</v>
-      </c>
-      <c r="J55" t="n">
-        <v>57</v>
-      </c>
-      <c r="K55" s="6" t="n">
-        <v>0.8116</v>
-      </c>
-      <c r="L55" s="6" t="n">
-        <v>0.8260999999999999</v>
-      </c>
-      <c r="M55" s="6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>unchanged</t>
-        </is>
-      </c>
-      <c r="O55" s="6" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v>0.8267</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="R55" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=69)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Southern Europe</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>free-wifi-offer</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Wi-Fi Package</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H56" t="n">
-        <v>69</v>
-      </c>
-      <c r="I56" t="n">
-        <v>56</v>
-      </c>
-      <c r="J56" t="n">
-        <v>57</v>
-      </c>
-      <c r="K56" s="6" t="n">
-        <v>0.8116</v>
-      </c>
-      <c r="L56" s="6" t="n">
-        <v>0.8260999999999999</v>
-      </c>
-      <c r="M56" s="6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>unchanged</t>
-        </is>
-      </c>
-      <c r="O56" s="6" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v>0.8267</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="R56" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=69)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Southern Europe</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>prepaid-service-charges</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Prepaid Service Charges</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
-        <v>69</v>
-      </c>
-      <c r="I57" t="n">
-        <v>56</v>
-      </c>
-      <c r="J57" t="n">
-        <v>57</v>
-      </c>
-      <c r="K57" s="6" t="n">
-        <v>0.8116</v>
-      </c>
-      <c r="L57" s="6" t="n">
-        <v>0.8260999999999999</v>
-      </c>
-      <c r="M57" s="6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>unchanged</t>
-        </is>
-      </c>
-      <c r="O57" s="6" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v>0.8267</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="R57" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=69)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Southern Europe</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>specialty-dining-offer</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Dining</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Removable</t>
-        </is>
-      </c>
-      <c r="H58" t="n">
-        <v>69</v>
-      </c>
-      <c r="I58" t="n">
-        <v>56</v>
-      </c>
-      <c r="J58" t="n">
-        <v>57</v>
-      </c>
-      <c r="K58" s="6" t="n">
-        <v>0.8116</v>
-      </c>
-      <c r="L58" s="6" t="n">
-        <v>0.8260999999999999</v>
-      </c>
-      <c r="M58" s="6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>unchanged</t>
-        </is>
-      </c>
-      <c r="O58" s="6" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v>0.8267</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="R58" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=69)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Southern Europe</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>specialty-dining-offer-7-8-nights</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Dining</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Removable</t>
-        </is>
-      </c>
-      <c r="H59" t="n">
-        <v>69</v>
-      </c>
-      <c r="I59" t="n">
-        <v>41</v>
-      </c>
-      <c r="J59" t="n">
-        <v>42</v>
-      </c>
-      <c r="K59" s="6" t="n">
-        <v>0.5942</v>
-      </c>
-      <c r="L59" s="6" t="n">
-        <v>0.6087</v>
-      </c>
-      <c r="M59" s="6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>unchanged</t>
-        </is>
-      </c>
-      <c r="O59" s="6" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="P59" s="6" t="n">
-        <v>0.6267</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>-1.28</v>
-      </c>
-      <c r="R59" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=69)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Southern Europe</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>specialty-dining-offer-9-nights</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Dining</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Removable</t>
-        </is>
-      </c>
-      <c r="H60" t="n">
-        <v>69</v>
-      </c>
-      <c r="I60" t="n">
-        <v>15</v>
-      </c>
-      <c r="J60" t="n">
-        <v>15</v>
-      </c>
-      <c r="K60" s="6" t="n">
-        <v>0.2174</v>
-      </c>
-      <c r="L60" s="6" t="n">
-        <v>0.2174</v>
-      </c>
-      <c r="M60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>unchanged</t>
-        </is>
-      </c>
-      <c r="O60" s="6" t="n">
-        <v>0.1875</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="R60" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=69)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Southern Europe</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>travel-protection-essentials</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Travel Protection | Essentials</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H61" t="n">
-        <v>69</v>
-      </c>
-      <c r="I61" t="n">
-        <v>56</v>
-      </c>
-      <c r="J61" t="n">
-        <v>57</v>
-      </c>
-      <c r="K61" s="6" t="n">
-        <v>0.8116</v>
-      </c>
-      <c r="L61" s="6" t="n">
-        <v>0.8260999999999999</v>
-      </c>
-      <c r="M61" s="6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>unchanged</t>
-        </is>
-      </c>
-      <c r="O61" s="6" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v>0.8267</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="R61" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=69)</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Southern Europe</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>travel-protection-norwegiancare</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Travel Protection | NorwegianCare</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="H62" t="n">
-        <v>69</v>
-      </c>
-      <c r="I62" t="n">
-        <v>56</v>
-      </c>
-      <c r="J62" t="n">
-        <v>57</v>
-      </c>
-      <c r="K62" s="6" t="n">
-        <v>0.8116</v>
-      </c>
-      <c r="L62" s="6" t="n">
-        <v>0.8260999999999999</v>
-      </c>
-      <c r="M62" s="6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>unchanged</t>
-        </is>
-      </c>
-      <c r="O62" s="6" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v>0.8267</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="R62" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=69)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Southern Europe</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>unlimited-open-bar-offer</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Bar</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Removable</t>
-        </is>
-      </c>
-      <c r="H63" t="n">
-        <v>69</v>
-      </c>
-      <c r="I63" t="n">
-        <v>56</v>
-      </c>
-      <c r="J63" t="n">
-        <v>57</v>
-      </c>
-      <c r="K63" s="6" t="n">
-        <v>0.8116</v>
-      </c>
-      <c r="L63" s="6" t="n">
-        <v>0.8260999999999999</v>
-      </c>
-      <c r="M63" s="6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>unchanged</t>
-        </is>
-      </c>
-      <c r="O63" s="6" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v>0.8267</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="R63" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=69)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A15:R63"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>